--- a/out/step_count.xlsx
+++ b/out/step_count.xlsx
@@ -355,7 +355,7 @@
     <row r="2" ht="16.0" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象: /c/Users/taka_/Claude/Step_Count_Tool/sample    計測日時: 2026-09-19 08:30:16    有効ステップ = 総行数 - 空白行 - コメント行</t>
+          <t xml:space="preserve">対象: /c/Users/taka_/Claude/Step_Count_Tool/sample    計測日時: 2026-09-23 15:46:02    有効ステップ = 総行数 - 空白行 - コメント行</t>
         </is>
       </c>
       <c r="C2" s="2"/>
@@ -420,22 +420,22 @@
     </row>
     <row r="7" ht="34.0" customHeight="1">
       <c r="B7" s="25">
-        <v>749</v>
+        <v>616</v>
       </c>
       <c r="C7" s="25">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25">
-        <v>1058</v>
+        <v>872</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="0"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-19 08:30:16</t>
+          <t xml:space="preserve">2026-09-23 15:46:02</t>
         </is>
       </c>
       <c r="D11" s="23"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">実施 (検出ブロック数: 81)</t>
+          <t xml:space="preserve">実施 (検出ブロック数: 52)</t>
         </is>
       </c>
       <c r="D17" s="23"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">実施 / 中央値 (推測ファイル数: 5)</t>
+          <t xml:space="preserve">実施 / 基準環境 terraform/stacks/j1 の実測値 (推測ファイル数: 8)</t>
         </is>
       </c>
       <c r="D18" s="23"/>
@@ -640,12 +640,12 @@
     <row r="19" ht="18.0" customHeight="1">
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境ディレクトリ</t>
+          <t xml:space="preserve">推測の判定</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,j3,st,pr</t>
+          <t xml:space="preserve">j2: 推測なし (6 ファイル / j1: 6 ファイル)    j3: 2 件推測 (4 ファイル / j1: 6 ファイル)    st: 6 件推測 (0 ファイル / j1: 6 ファイル)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D19" s="23"/>
@@ -660,12 +660,12 @@
     <row r="20" ht="18.0" customHeight="1">
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効ステップ数の定義</t>
+          <t xml:space="preserve">推測の対象外</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効ステップ = 総行数 - 空白行 - コメント行</t>
+          <t xml:space="preserve">containers 配下 / terraform/stacks 以外の環境ディレクトリ</t>
         </is>
       </c>
       <c r="D20" s="23"/>
@@ -680,12 +680,12 @@
     <row r="21" ht="18.0" customHeight="1">
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成ツール</t>
+          <t xml:space="preserve">環境ディレクトリ</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">step_count.sh 1.0.0</t>
+          <t xml:space="preserve">j1,j2,j3,st</t>
         </is>
       </c>
       <c r="D21" s="23"/>
@@ -697,386 +697,358 @@
       <c r="J21" s="23"/>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="8" customHeight="1"/>
-    <row r="23" ht="26.0" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="22" ht="18.0" customHeight="1">
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効ステップ数の定義</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効ステップ = 総行数 - 空白行 - コメント行</t>
+        </is>
+      </c>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" ht="18.0" customHeight="1">
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成ツール</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">step_count.sh 1.0.0</t>
+        </is>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="26.0" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3.  拡張子別 集計</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" ht="30.0" customHeight="1">
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" ht="30.0" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">拡張子</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイル数</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">総行数</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">空白行数</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コメント行数</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コード行数</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">有効ステップ数</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">構成比</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ファイル数</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ステップ数</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="C25" s="8">
-        <v>11</v>
-      </c>
-      <c r="D25" s="8">
-        <v>303</v>
-      </c>
-      <c r="E25" s="8">
-        <v>65</v>
-      </c>
-      <c r="F25" s="8">
-        <v>31</v>
-      </c>
-      <c r="G25" s="8">
-        <v>207</v>
-      </c>
-      <c r="H25" s="8">
-        <v>207</v>
-      </c>
-      <c r="I25" s="12">
-        <v>0.276368</v>
-      </c>
-      <c r="J25" s="8">
-        <v>2</v>
-      </c>
-      <c r="K25" s="8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+      <c r="C27" s="8">
+        <v>12</v>
+      </c>
+      <c r="D27" s="8">
+        <v>266</v>
+      </c>
+      <c r="E27" s="8">
+        <v>57</v>
+      </c>
+      <c r="F27" s="8">
+        <v>28</v>
+      </c>
+      <c r="G27" s="8">
+        <v>181</v>
+      </c>
+      <c r="H27" s="8">
+        <v>181</v>
+      </c>
+      <c r="I27" s="12">
+        <v>0.293831</v>
+      </c>
+      <c r="J27" s="8">
+        <v>3</v>
+      </c>
+      <c r="K27" s="8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="C26" s="9">
-        <v>20</v>
-      </c>
-      <c r="D26" s="9">
-        <v>755</v>
-      </c>
-      <c r="E26" s="9">
-        <v>152</v>
-      </c>
-      <c r="F26" s="9">
-        <v>61</v>
-      </c>
-      <c r="G26" s="9">
-        <v>542</v>
-      </c>
-      <c r="H26" s="9">
-        <v>542</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0.723632</v>
-      </c>
-      <c r="J26" s="9">
-        <v>3</v>
-      </c>
-      <c r="K26" s="9">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" ht="20.0" customHeight="1">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="C28" s="9">
+        <v>16</v>
+      </c>
+      <c r="D28" s="9">
+        <v>606</v>
+      </c>
+      <c r="E28" s="9">
+        <v>122</v>
+      </c>
+      <c r="F28" s="9">
+        <v>49</v>
+      </c>
+      <c r="G28" s="9">
+        <v>435</v>
+      </c>
+      <c r="H28" s="9">
+        <v>435</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0.706169</v>
+      </c>
+      <c r="J28" s="9">
+        <v>5</v>
+      </c>
+      <c r="K28" s="9">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" ht="20.0" customHeight="1">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="C27" s="15">
-        <v>31</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1058</v>
-      </c>
-      <c r="E27" s="15">
-        <v>217</v>
-      </c>
-      <c r="F27" s="15">
-        <v>92</v>
-      </c>
-      <c r="G27" s="15">
-        <v>749</v>
-      </c>
-      <c r="H27" s="15">
-        <v>749</v>
-      </c>
-      <c r="I27" s="17">
+      <c r="C29" s="15">
+        <v>28</v>
+      </c>
+      <c r="D29" s="15">
+        <v>872</v>
+      </c>
+      <c r="E29" s="15">
+        <v>179</v>
+      </c>
+      <c r="F29" s="15">
+        <v>77</v>
+      </c>
+      <c r="G29" s="15">
+        <v>616</v>
+      </c>
+      <c r="H29" s="15">
+        <v>616</v>
+      </c>
+      <c r="I29" s="17">
         <v>1.000000</v>
       </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
-      <c r="K27" s="15">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="26.0" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="J29" s="15">
+        <v>8</v>
+      </c>
+      <c r="K29" s="15">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="26.0" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4.  環境別 集計</t>
         </is>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" ht="30.0" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" ht="30.0" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">環境</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイル数</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">総行数</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">空白行数</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コメント行数</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コード行数</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">有効ステップ数</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">構成比</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ファイル数</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ステップ数</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1</t>
-        </is>
-      </c>
-      <c r="C31" s="8">
-        <v>6</v>
-      </c>
-      <c r="D31" s="8">
-        <v>209</v>
-      </c>
-      <c r="E31" s="8">
-        <v>43</v>
-      </c>
-      <c r="F31" s="8">
-        <v>18</v>
-      </c>
-      <c r="G31" s="8">
-        <v>148</v>
-      </c>
-      <c r="H31" s="8">
-        <v>148</v>
-      </c>
-      <c r="I31" s="12">
-        <v>0.197597</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j2</t>
-        </is>
-      </c>
-      <c r="C32" s="9">
-        <v>6</v>
-      </c>
-      <c r="D32" s="9">
-        <v>219</v>
-      </c>
-      <c r="E32" s="9">
-        <v>45</v>
-      </c>
-      <c r="F32" s="9">
-        <v>19</v>
-      </c>
-      <c r="G32" s="9">
-        <v>155</v>
-      </c>
-      <c r="H32" s="9">
-        <v>155</v>
-      </c>
-      <c r="I32" s="13">
-        <v>0.206943</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="C33" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33" s="8">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E33" s="8">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F33" s="8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G33" s="8">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H33" s="8">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I33" s="12">
-        <v>0.197597</v>
+        <v>0.254870</v>
       </c>
       <c r="J33" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">st</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="C34" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="9">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="E34" s="9">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F34" s="9">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G34" s="9">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="H34" s="9">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="I34" s="13">
-        <v>0.197597</v>
+        <v>0.261364</v>
       </c>
       <c r="J34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="9">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr</t>
+          <t xml:space="preserve">j3</t>
         </is>
       </c>
       <c r="C35" s="8">
@@ -1098,215 +1070,233 @@
         <v>148</v>
       </c>
       <c r="I35" s="12">
-        <v>0.197597</v>
+        <v>0.240260</v>
       </c>
       <c r="J35" s="8">
         <v>2</v>
       </c>
       <c r="K35" s="8">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="C36" s="9">
+        <v>6</v>
+      </c>
+      <c r="D36" s="9">
+        <v>209</v>
+      </c>
+      <c r="E36" s="9">
+        <v>43</v>
+      </c>
+      <c r="F36" s="9">
+        <v>18</v>
+      </c>
+      <c r="G36" s="9">
+        <v>148</v>
+      </c>
+      <c r="H36" s="9">
+        <v>148</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0.240260</v>
+      </c>
+      <c r="J36" s="9">
+        <v>6</v>
+      </c>
+      <c r="K36" s="9">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">(環境ディレクトリ外)</t>
         </is>
       </c>
-      <c r="C36" s="9">
+      <c r="C37" s="8">
         <v>1</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D37" s="8">
         <v>3</v>
       </c>
-      <c r="E36" s="9">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
         <v>1</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G37" s="8">
         <v>2</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H37" s="8">
         <v>2</v>
       </c>
-      <c r="I36" s="13">
-        <v>0.002670</v>
-      </c>
-      <c r="J36" s="9">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="20.0" customHeight="1">
-      <c r="B37" s="14" t="inlineStr">
+      <c r="I37" s="12">
+        <v>0.003247</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="20.0" customHeight="1">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="C37" s="15">
-        <v>31</v>
-      </c>
-      <c r="D37" s="15">
-        <v>1058</v>
-      </c>
-      <c r="E37" s="15">
-        <v>217</v>
-      </c>
-      <c r="F37" s="15">
-        <v>92</v>
-      </c>
-      <c r="G37" s="15">
-        <v>749</v>
-      </c>
-      <c r="H37" s="15">
-        <v>749</v>
-      </c>
-      <c r="I37" s="17">
+      <c r="C38" s="15">
+        <v>28</v>
+      </c>
+      <c r="D38" s="15">
+        <v>872</v>
+      </c>
+      <c r="E38" s="15">
+        <v>179</v>
+      </c>
+      <c r="F38" s="15">
+        <v>77</v>
+      </c>
+      <c r="G38" s="15">
+        <v>616</v>
+      </c>
+      <c r="H38" s="15">
+        <v>616</v>
+      </c>
+      <c r="I38" s="17">
         <v>1.000000</v>
       </c>
-      <c r="J37" s="15">
-        <v>5</v>
-      </c>
-      <c r="K37" s="15">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" ht="8" customHeight="1"/>
-    <row r="39" ht="26.0" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="J38" s="15">
+        <v>8</v>
+      </c>
+      <c r="K38" s="15">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="26.0" customHeight="1">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5.  環境 x 拡張子 別 有効ステップ数</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-    </row>
-    <row r="40" ht="30.0" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">環境</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">j1</t>
         </is>
       </c>
-      <c r="C41" s="8">
+      <c r="C42" s="8">
+        <v>50</v>
+      </c>
+      <c r="D42" s="8">
+        <v>107</v>
+      </c>
+      <c r="E42" s="8">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="C43" s="9">
+        <v>47</v>
+      </c>
+      <c r="D43" s="9">
+        <v>114</v>
+      </c>
+      <c r="E43" s="9">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="C44" s="8">
         <v>41</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D44" s="8">
         <v>107</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E44" s="8">
         <v>148</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j2</t>
-        </is>
-      </c>
-      <c r="C42" s="9">
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="C45" s="9">
         <v>41</v>
       </c>
-      <c r="D42" s="9">
-        <v>114</v>
-      </c>
-      <c r="E42" s="9">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="C43" s="8">
-        <v>41</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="D45" s="9">
         <v>107</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E45" s="9">
         <v>148</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="C44" s="9">
-        <v>41</v>
-      </c>
-      <c r="D44" s="9">
-        <v>107</v>
-      </c>
-      <c r="E44" s="9">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="C45" s="8">
-        <v>41</v>
-      </c>
-      <c r="D45" s="8">
-        <v>107</v>
-      </c>
-      <c r="E45" s="8">
-        <v>148</v>
-      </c>
-    </row>
     <row r="46">
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(環境ディレクトリ外)</t>
         </is>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>2</v>
       </c>
-      <c r="D46" s="9">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9">
+      <c r="D46" s="8">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8">
         <v>2</v>
       </c>
     </row>
@@ -1317,18 +1307,18 @@
         </is>
       </c>
       <c r="C47" s="15">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="D47" s="15">
-        <v>542</v>
+        <v>435</v>
       </c>
       <c r="E47" s="15">
-        <v>749</v>
+        <v>616</v>
       </c>
     </row>
     <row r="48" ht="8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:K4"/>
@@ -1353,11 +1343,13 @@
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C21:K21"/>
-    <mergeCell ref="B23:K23"/>
-    <mergeCell ref="B29:K29"/>
-    <mergeCell ref="B39:K39"/>
+    <mergeCell ref="C22:K22"/>
+    <mergeCell ref="C23:K23"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="B40:K40"/>
   </mergeCells>
-  <conditionalFormatting sqref="H25:H26">
+  <conditionalFormatting sqref="H27:H28">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1366,7 +1358,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H36">
+  <conditionalFormatting sqref="H33:H37">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1375,7 +1367,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41:E46">
+  <conditionalFormatting sqref="E42:E46">
     <cfRule type="dataBar" priority="3">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1407,7 +1399,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="10" max="10" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1503,12 +1495,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">containers/j1/app/entrypoint.sh</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -1517,19 +1509,19 @@
         </is>
       </c>
       <c r="E5" s="8">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F5" s="8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="8">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I5" s="8">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1541,12 +1533,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/main.tf</t>
+          <t xml:space="preserve">containers/j1/app/healthcheck.sh</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1555,19 +1547,19 @@
         </is>
       </c>
       <c r="E6" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
       </c>
       <c r="H6" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -1579,7 +1571,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1617,7 +1609,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1631,19 +1623,19 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F8" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G8" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H8" s="9">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="I8" s="9">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="J8" s="7"/>
     </row>
@@ -1655,12 +1647,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1669,19 +1661,19 @@
         </is>
       </c>
       <c r="E9" s="8">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="F9" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
       </c>
       <c r="H9" s="8">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I9" s="8">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1693,12 +1685,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/scripts/deploy.sh</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1707,36 +1699,36 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F10" s="9">
+        <v>10</v>
+      </c>
+      <c r="G10" s="9">
         <v>9</v>
       </c>
-      <c r="G10" s="9">
-        <v>5</v>
-      </c>
       <c r="H10" s="9">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="I10" s="9">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J10" s="7"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1745,36 +1737,36 @@
         </is>
       </c>
       <c r="E11" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F11" s="8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
       </c>
       <c r="H11" s="8">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I11" s="8">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J11" s="6"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/scripts/deploy.sh</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1783,19 +1775,19 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F12" s="9">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G12" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" s="9">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I12" s="9">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="J12" s="7"/>
     </row>
@@ -1807,12 +1799,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">containers/j2/app/entrypoint.sh</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1821,19 +1813,19 @@
         </is>
       </c>
       <c r="E13" s="8">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F13" s="8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
       </c>
       <c r="H13" s="8">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I13" s="8">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -1845,7 +1837,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1859,19 +1851,19 @@
         </is>
       </c>
       <c r="E14" s="9">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="F14" s="9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G14" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H14" s="9">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="I14" s="9">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J14" s="7"/>
     </row>
@@ -1883,12 +1875,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1897,19 +1889,19 @@
         </is>
       </c>
       <c r="E15" s="8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F15" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="8">
         <v>1</v>
       </c>
       <c r="H15" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I15" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -1921,12 +1913,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/scripts/deploy.sh</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1935,78 +1927,74 @@
         </is>
       </c>
       <c r="E16" s="9">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F16" s="9">
         <v>9</v>
       </c>
       <c r="G16" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I16" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J16" s="7"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測</t>
-        </is>
-      </c>
-      <c r="E17" s="19">
-        <v>40</v>
-      </c>
-      <c r="F17" s="19">
-        <v>9</v>
-      </c>
-      <c r="G17" s="19">
-        <v>1</v>
-      </c>
-      <c r="H17" s="19">
-        <v>30</v>
-      </c>
-      <c r="I17" s="19">
-        <v>30</v>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1,j2,st,pr の中央値 (4環境)</t>
-        </is>
-      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E17" s="8">
+        <v>69</v>
+      </c>
+      <c r="F17" s="8">
+        <v>12</v>
+      </c>
+      <c r="G17" s="8">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8">
+        <v>47</v>
+      </c>
+      <c r="I17" s="8">
+        <v>47</v>
+      </c>
+      <c r="J17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -2015,36 +2003,36 @@
         </is>
       </c>
       <c r="E18" s="9">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F18" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
       </c>
       <c r="H18" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I18" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J18" s="7"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/scripts/deploy.sh</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -2053,101 +2041,101 @@
         </is>
       </c>
       <c r="E19" s="8">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19" s="8">
         <v>9</v>
       </c>
       <c r="G19" s="8">
+        <v>5</v>
+      </c>
+      <c r="H19" s="8">
+        <v>29</v>
+      </c>
+      <c r="I19" s="8">
+        <v>29</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j3/compute/ec2.tf</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E20" s="21">
+        <v>40</v>
+      </c>
+      <c r="F20" s="21">
+        <v>9</v>
+      </c>
+      <c r="G20" s="21">
         <v>1</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H20" s="21">
         <v>30</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I20" s="21">
         <v>30</v>
       </c>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">j3</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">実測</t>
         </is>
       </c>
-      <c r="E20" s="9">
-        <v>59</v>
-      </c>
-      <c r="F20" s="9">
+      <c r="E21" s="8">
         <v>10</v>
       </c>
-      <c r="G20" s="9">
-        <v>9</v>
-      </c>
-      <c r="H20" s="9">
-        <v>40</v>
-      </c>
-      <c r="I20" s="9">
-        <v>40</v>
-      </c>
-      <c r="J20" s="7"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3/scripts/backup.sh</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測</t>
-        </is>
-      </c>
-      <c r="E21" s="19">
-        <v>17</v>
-      </c>
-      <c r="F21" s="19">
-        <v>4</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+      <c r="G21" s="8">
         <v>1</v>
       </c>
-      <c r="H21" s="19">
-        <v>12</v>
-      </c>
-      <c r="I21" s="19">
-        <v>12</v>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1,j2,st の中央値 (3環境)</t>
-        </is>
-      </c>
+      <c r="H21" s="8">
+        <v>7</v>
+      </c>
+      <c r="I21" s="8">
+        <v>7</v>
+      </c>
+      <c r="J21" s="6"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2157,12 +2145,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/scripts/deploy.sh</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -2171,306 +2159,322 @@
         </is>
       </c>
       <c r="E22" s="9">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F22" s="9">
         <v>9</v>
       </c>
       <c r="G22" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="7"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E23" s="8">
+        <v>59</v>
+      </c>
+      <c r="F23" s="8">
+        <v>10</v>
+      </c>
+      <c r="G23" s="8">
+        <v>9</v>
+      </c>
+      <c r="H23" s="8">
+        <v>40</v>
+      </c>
+      <c r="I23" s="8">
+        <v>40</v>
+      </c>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j3/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E24" s="21">
+        <v>17</v>
+      </c>
+      <c r="F24" s="21">
+        <v>4</v>
+      </c>
+      <c r="G24" s="21">
+        <v>1</v>
+      </c>
+      <c r="H24" s="21">
+        <v>12</v>
+      </c>
+      <c r="I24" s="21">
+        <v>12</v>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/j3/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E25" s="8">
+        <v>43</v>
+      </c>
+      <c r="F25" s="8">
+        <v>9</v>
+      </c>
+      <c r="G25" s="8">
+        <v>5</v>
+      </c>
+      <c r="H25" s="8">
+        <v>29</v>
+      </c>
+      <c r="I25" s="8">
+        <v>29</v>
+      </c>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/compute/ec2.tf</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E23" s="8">
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E26" s="21">
         <v>40</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F26" s="21">
         <v>9</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G26" s="21">
         <v>1</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H26" s="21">
         <v>30</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I26" s="21">
         <v>30</v>
       </c>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/main.tf</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E24" s="9">
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E27" s="19">
         <v>10</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F27" s="19">
         <v>2</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G27" s="19">
         <v>1</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H27" s="19">
         <v>7</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I27" s="19">
         <v>7</v>
       </c>
-      <c r="J24" s="7"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/main.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E25" s="19">
+      <c r="E28" s="21">
         <v>40</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F28" s="21">
         <v>9</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G28" s="21">
         <v>1</v>
       </c>
-      <c r="H25" s="19">
+      <c r="H28" s="21">
         <v>30</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I28" s="21">
         <v>30</v>
       </c>
-      <c r="J25" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1,j2,j3,pr の中央値 (4環境)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/subnet.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E26" s="9">
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E29" s="19">
         <v>59</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F29" s="19">
         <v>10</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G29" s="19">
         <v>9</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H29" s="19">
         <v>40</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I29" s="19">
         <v>40</v>
       </c>
-      <c r="J26" s="7"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/scripts/backup.sh</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E27" s="8">
-        <v>17</v>
-      </c>
-      <c r="F27" s="8">
-        <v>4</v>
-      </c>
-      <c r="G27" s="8">
-        <v>1</v>
-      </c>
-      <c r="H27" s="8">
-        <v>12</v>
-      </c>
-      <c r="I27" s="8">
-        <v>12</v>
-      </c>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/scripts/deploy.sh</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E28" s="9">
-        <v>43</v>
-      </c>
-      <c r="F28" s="9">
-        <v>9</v>
-      </c>
-      <c r="G28" s="9">
-        <v>5</v>
-      </c>
-      <c r="H28" s="9">
-        <v>29</v>
-      </c>
-      <c r="I28" s="9">
-        <v>29</v>
-      </c>
-      <c r="J28" s="7"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E29" s="8">
-        <v>40</v>
-      </c>
-      <c r="F29" s="8">
-        <v>9</v>
-      </c>
-      <c r="G29" s="8">
-        <v>1</v>
-      </c>
-      <c r="H29" s="8">
-        <v>30</v>
-      </c>
-      <c r="I29" s="8">
-        <v>30</v>
-      </c>
-      <c r="J29" s="6"/>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/vpc.tf)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr</t>
+          <t xml:space="preserve">st</t>
         </is>
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/st/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
@@ -2479,78 +2483,82 @@
         </is>
       </c>
       <c r="E30" s="21">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F30" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="21">
         <v>1</v>
       </c>
       <c r="H30" s="21">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I30" s="21">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,j3,st の中央値 (4環境)</t>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E31" s="8">
-        <v>40</v>
-      </c>
-      <c r="F31" s="8">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E31" s="19">
+        <v>43</v>
+      </c>
+      <c r="F31" s="19">
         <v>9</v>
       </c>
-      <c r="G31" s="8">
-        <v>1</v>
-      </c>
-      <c r="H31" s="8">
-        <v>30</v>
-      </c>
-      <c r="I31" s="8">
-        <v>30</v>
-      </c>
-      <c r="J31" s="6"/>
+      <c r="G31" s="19">
+        <v>5</v>
+      </c>
+      <c r="H31" s="19">
+        <v>29</v>
+      </c>
+      <c r="I31" s="19">
+        <v>29</v>
+      </c>
+      <c r="J31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/deploy.sh)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr</t>
+          <t xml:space="preserve">(環境外)</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
+          <t xml:space="preserve">common/README.sh</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -2559,177 +2567,59 @@
         </is>
       </c>
       <c r="E32" s="9">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="F32" s="9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G32" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H32" s="9">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I32" s="9">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J32" s="7"/>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/scripts/backup.sh</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測</t>
-        </is>
-      </c>
-      <c r="E33" s="19">
-        <v>17</v>
-      </c>
-      <c r="F33" s="19">
-        <v>4</v>
-      </c>
-      <c r="G33" s="19">
-        <v>1</v>
-      </c>
-      <c r="H33" s="19">
-        <v>12</v>
-      </c>
-      <c r="I33" s="19">
-        <v>12</v>
-      </c>
-      <c r="J33" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1,j2,st の中央値 (3環境)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/scripts/deploy.sh</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E34" s="9">
-        <v>43</v>
-      </c>
-      <c r="F34" s="9">
-        <v>9</v>
-      </c>
-      <c r="G34" s="9">
-        <v>5</v>
-      </c>
-      <c r="H34" s="9">
-        <v>29</v>
-      </c>
-      <c r="I34" s="9">
-        <v>29</v>
-      </c>
-      <c r="J34" s="7"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(環境外)</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">common/README.sh</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E35" s="8">
-        <v>3</v>
-      </c>
-      <c r="F35" s="8">
-        <v>0</v>
-      </c>
-      <c r="G35" s="8">
-        <v>1</v>
-      </c>
-      <c r="H35" s="8">
-        <v>2</v>
-      </c>
-      <c r="I35" s="8">
-        <v>2</v>
-      </c>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31 件</t>
-        </is>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="15">
-        <v>1058</v>
-      </c>
-      <c r="F36" s="15">
-        <v>217</v>
-      </c>
-      <c r="G36" s="15">
-        <v>92</v>
-      </c>
-      <c r="H36" s="15">
-        <v>749</v>
-      </c>
-      <c r="I36" s="15">
-        <v>749</v>
-      </c>
-      <c r="J36" s="14"/>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 件</t>
+        </is>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="15">
+        <v>872</v>
+      </c>
+      <c r="F33" s="15">
+        <v>179</v>
+      </c>
+      <c r="G33" s="15">
+        <v>77</v>
+      </c>
+      <c r="H33" s="15">
+        <v>616</v>
+      </c>
+      <c r="I33" s="15">
+        <v>616</v>
+      </c>
+      <c r="J33" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J35"/>
+  <autoFilter ref="A4:J32"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I35">
+  <conditionalFormatting sqref="I5:I32">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2873,7 +2763,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -2917,7 +2807,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2965,7 +2855,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -3013,7 +2903,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3061,7 +2951,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -3109,7 +2999,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -3153,7 +3043,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -3201,7 +3091,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -3249,7 +3139,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -3293,7 +3183,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -3341,7 +3231,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -3389,7 +3279,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -3437,7 +3327,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -3485,7 +3375,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -3533,7 +3423,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -3577,7 +3467,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -3625,7 +3515,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -3673,7 +3563,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -3721,7 +3611,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -3769,7 +3659,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -3817,7 +3707,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3865,7 +3755,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -3913,7 +3803,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -3957,7 +3847,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -4005,7 +3895,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -4053,7 +3943,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -4101,7 +3991,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -4149,7 +4039,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -4193,7 +4083,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -4241,7 +4131,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -4289,7 +4179,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -4333,7 +4223,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
@@ -4381,7 +4271,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -4429,7 +4319,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -4477,7 +4367,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -4525,7 +4415,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -4573,7 +4463,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -4617,7 +4507,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -4665,7 +4555,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -4713,7 +4603,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -4761,7 +4651,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -4809,7 +4699,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -4857,7 +4747,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4905,7 +4795,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -4953,7 +4843,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -5001,7 +4891,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -5049,7 +4939,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -5093,7 +4983,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
@@ -5141,7 +5031,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -5189,7 +5079,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -5233,7 +5123,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -5281,7 +5171,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
@@ -5329,7 +5219,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -5377,7 +5267,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
@@ -5425,7 +5315,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5473,7 +5363,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
@@ -5517,7 +5407,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -5565,7 +5455,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
@@ -5613,7 +5503,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5661,7 +5551,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -5709,7 +5599,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -5757,7 +5647,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
@@ -5805,7 +5695,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -5845,1701 +5735,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9">
-        <v>5</v>
-      </c>
-      <c r="I68" s="9">
-        <v>4</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9">
-        <v>0</v>
-      </c>
-      <c r="L68" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">data</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_ami</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amazon_linux</t>
-        </is>
-      </c>
-      <c r="F69" s="8">
-        <v>3</v>
-      </c>
-      <c r="G69" s="8">
-        <v>11</v>
-      </c>
-      <c r="H69" s="8">
-        <v>9</v>
-      </c>
-      <c r="I69" s="8">
-        <v>1</v>
-      </c>
-      <c r="J69" s="8">
-        <v>0</v>
-      </c>
-      <c r="K69" s="8">
-        <v>8</v>
-      </c>
-      <c r="L69" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_instance</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">app</t>
-        </is>
-      </c>
-      <c r="F70" s="9">
-        <v>13</v>
-      </c>
-      <c r="G70" s="9">
-        <v>28</v>
-      </c>
-      <c r="H70" s="9">
-        <v>16</v>
-      </c>
-      <c r="I70" s="9">
-        <v>3</v>
-      </c>
-      <c r="J70" s="9">
-        <v>0</v>
-      </c>
-      <c r="K70" s="9">
-        <v>13</v>
-      </c>
-      <c r="L70" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">module</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alb</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F71" s="8">
-        <v>30</v>
-      </c>
-      <c r="G71" s="8">
-        <v>35</v>
-      </c>
-      <c r="H71" s="8">
-        <v>6</v>
-      </c>
-      <c r="I71" s="8">
-        <v>1</v>
-      </c>
-      <c r="J71" s="8">
-        <v>0</v>
-      </c>
-      <c r="K71" s="8">
-        <v>5</v>
-      </c>
-      <c r="L71" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">instance_type</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F72" s="9">
-        <v>37</v>
-      </c>
-      <c r="G72" s="9">
-        <v>40</v>
-      </c>
-      <c r="H72" s="9">
-        <v>4</v>
-      </c>
-      <c r="I72" s="9">
-        <v>0</v>
-      </c>
-      <c r="J72" s="9">
-        <v>0</v>
-      </c>
-      <c r="K72" s="9">
-        <v>4</v>
-      </c>
-      <c r="L72" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/main.tf</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8">
-        <v>3</v>
-      </c>
-      <c r="I73" s="8">
-        <v>2</v>
-      </c>
-      <c r="J73" s="8">
-        <v>1</v>
-      </c>
-      <c r="K73" s="8">
-        <v>0</v>
-      </c>
-      <c r="L73" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/main.tf</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">provider</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F74" s="9">
-        <v>3</v>
-      </c>
-      <c r="G74" s="9">
-        <v>5</v>
-      </c>
-      <c r="H74" s="9">
-        <v>3</v>
-      </c>
-      <c r="I74" s="9">
-        <v>0</v>
-      </c>
-      <c r="J74" s="9">
-        <v>0</v>
-      </c>
-      <c r="K74" s="9">
-        <v>3</v>
-      </c>
-      <c r="L74" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/main.tf</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">region</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F75" s="8">
-        <v>7</v>
-      </c>
-      <c r="G75" s="8">
-        <v>10</v>
-      </c>
-      <c r="H75" s="8">
-        <v>4</v>
-      </c>
-      <c r="I75" s="8">
-        <v>0</v>
-      </c>
-      <c r="J75" s="8">
-        <v>0</v>
-      </c>
-      <c r="K75" s="8">
-        <v>4</v>
-      </c>
-      <c r="L75" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9">
-        <v>10</v>
-      </c>
-      <c r="I76" s="9">
-        <v>7</v>
-      </c>
-      <c r="J76" s="9">
-        <v>3</v>
-      </c>
-      <c r="K76" s="9">
-        <v>0</v>
-      </c>
-      <c r="L76" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F77" s="8">
-        <v>5</v>
-      </c>
-      <c r="G77" s="8">
-        <v>14</v>
-      </c>
-      <c r="H77" s="8">
-        <v>10</v>
-      </c>
-      <c r="I77" s="8">
-        <v>1</v>
-      </c>
-      <c r="J77" s="8">
-        <v>0</v>
-      </c>
-      <c r="K77" s="8">
-        <v>9</v>
-      </c>
-      <c r="L77" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">locals</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F78" s="9">
-        <v>16</v>
-      </c>
-      <c r="G78" s="9">
-        <v>22</v>
-      </c>
-      <c r="H78" s="9">
-        <v>7</v>
-      </c>
-      <c r="I78" s="9">
-        <v>0</v>
-      </c>
-      <c r="J78" s="9">
-        <v>1</v>
-      </c>
-      <c r="K78" s="9">
-        <v>6</v>
-      </c>
-      <c r="L78" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_vpc</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F79" s="8">
-        <v>24</v>
-      </c>
-      <c r="G79" s="8">
-        <v>33</v>
-      </c>
-      <c r="H79" s="8">
-        <v>10</v>
-      </c>
-      <c r="I79" s="8">
-        <v>1</v>
-      </c>
-      <c r="J79" s="8">
-        <v>1</v>
-      </c>
-      <c r="K79" s="8">
-        <v>8</v>
-      </c>
-      <c r="L79" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_internet_gateway</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F80" s="9">
-        <v>35</v>
-      </c>
-      <c r="G80" s="9">
-        <v>45</v>
-      </c>
-      <c r="H80" s="9">
-        <v>11</v>
-      </c>
-      <c r="I80" s="9">
-        <v>1</v>
-      </c>
-      <c r="J80" s="9">
-        <v>4</v>
-      </c>
-      <c r="K80" s="9">
-        <v>6</v>
-      </c>
-      <c r="L80" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpc_cidr</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F81" s="8">
-        <v>47</v>
-      </c>
-      <c r="G81" s="8">
-        <v>51</v>
-      </c>
-      <c r="H81" s="8">
-        <v>5</v>
-      </c>
-      <c r="I81" s="8">
-        <v>0</v>
-      </c>
-      <c r="J81" s="8">
-        <v>0</v>
-      </c>
-      <c r="K81" s="8">
-        <v>5</v>
-      </c>
-      <c r="L81" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env_name</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F82" s="9">
-        <v>53</v>
-      </c>
-      <c r="G82" s="9">
-        <v>55</v>
-      </c>
-      <c r="H82" s="9">
-        <v>3</v>
-      </c>
-      <c r="I82" s="9">
-        <v>0</v>
-      </c>
-      <c r="J82" s="9">
-        <v>0</v>
-      </c>
-      <c r="K82" s="9">
-        <v>3</v>
-      </c>
-      <c r="L82" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">output</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpc_id</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F83" s="8">
-        <v>57</v>
-      </c>
-      <c r="G83" s="8">
-        <v>59</v>
-      </c>
-      <c r="H83" s="8">
-        <v>3</v>
-      </c>
-      <c r="I83" s="8">
-        <v>0</v>
-      </c>
-      <c r="J83" s="8">
-        <v>0</v>
-      </c>
-      <c r="K83" s="8">
-        <v>3</v>
-      </c>
-      <c r="L83" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9">
-        <v>5</v>
-      </c>
-      <c r="I84" s="9">
-        <v>4</v>
-      </c>
-      <c r="J84" s="9">
-        <v>1</v>
-      </c>
-      <c r="K84" s="9">
-        <v>0</v>
-      </c>
-      <c r="L84" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">data</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_ami</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amazon_linux</t>
-        </is>
-      </c>
-      <c r="F85" s="8">
-        <v>3</v>
-      </c>
-      <c r="G85" s="8">
-        <v>11</v>
-      </c>
-      <c r="H85" s="8">
-        <v>9</v>
-      </c>
-      <c r="I85" s="8">
-        <v>1</v>
-      </c>
-      <c r="J85" s="8">
-        <v>0</v>
-      </c>
-      <c r="K85" s="8">
-        <v>8</v>
-      </c>
-      <c r="L85" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_instance</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">app</t>
-        </is>
-      </c>
-      <c r="F86" s="9">
-        <v>13</v>
-      </c>
-      <c r="G86" s="9">
-        <v>28</v>
-      </c>
-      <c r="H86" s="9">
-        <v>16</v>
-      </c>
-      <c r="I86" s="9">
-        <v>3</v>
-      </c>
-      <c r="J86" s="9">
-        <v>0</v>
-      </c>
-      <c r="K86" s="9">
-        <v>13</v>
-      </c>
-      <c r="L86" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">module</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alb</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F87" s="8">
-        <v>30</v>
-      </c>
-      <c r="G87" s="8">
-        <v>35</v>
-      </c>
-      <c r="H87" s="8">
-        <v>6</v>
-      </c>
-      <c r="I87" s="8">
-        <v>1</v>
-      </c>
-      <c r="J87" s="8">
-        <v>0</v>
-      </c>
-      <c r="K87" s="8">
-        <v>5</v>
-      </c>
-      <c r="L87" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C88" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">instance_type</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F88" s="9">
-        <v>37</v>
-      </c>
-      <c r="G88" s="9">
-        <v>40</v>
-      </c>
-      <c r="H88" s="9">
-        <v>4</v>
-      </c>
-      <c r="I88" s="9">
-        <v>0</v>
-      </c>
-      <c r="J88" s="9">
-        <v>0</v>
-      </c>
-      <c r="K88" s="9">
-        <v>4</v>
-      </c>
-      <c r="L88" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8">
-        <v>6</v>
-      </c>
-      <c r="I89" s="8">
-        <v>5</v>
-      </c>
-      <c r="J89" s="8">
-        <v>1</v>
-      </c>
-      <c r="K89" s="8">
-        <v>0</v>
-      </c>
-      <c r="L89" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_subnet</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">public</t>
-        </is>
-      </c>
-      <c r="F90" s="9">
-        <v>3</v>
-      </c>
-      <c r="G90" s="9">
-        <v>13</v>
-      </c>
-      <c r="H90" s="9">
-        <v>11</v>
-      </c>
-      <c r="I90" s="9">
-        <v>2</v>
-      </c>
-      <c r="J90" s="9">
-        <v>0</v>
-      </c>
-      <c r="K90" s="9">
-        <v>9</v>
-      </c>
-      <c r="L90" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_subnet</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">private</t>
-        </is>
-      </c>
-      <c r="F91" s="8">
-        <v>15</v>
-      </c>
-      <c r="G91" s="8">
-        <v>25</v>
-      </c>
-      <c r="H91" s="8">
-        <v>11</v>
-      </c>
-      <c r="I91" s="8">
-        <v>2</v>
-      </c>
-      <c r="J91" s="8">
-        <v>0</v>
-      </c>
-      <c r="K91" s="8">
-        <v>9</v>
-      </c>
-      <c r="L91" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C92" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">public_subnets</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F92" s="9">
-        <v>27</v>
-      </c>
-      <c r="G92" s="9">
-        <v>30</v>
-      </c>
-      <c r="H92" s="9">
-        <v>4</v>
-      </c>
-      <c r="I92" s="9">
-        <v>0</v>
-      </c>
-      <c r="J92" s="9">
-        <v>0</v>
-      </c>
-      <c r="K92" s="9">
-        <v>4</v>
-      </c>
-      <c r="L92" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">private_subnets</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F93" s="8">
-        <v>32</v>
-      </c>
-      <c r="G93" s="8">
-        <v>35</v>
-      </c>
-      <c r="H93" s="8">
-        <v>4</v>
-      </c>
-      <c r="I93" s="8">
-        <v>0</v>
-      </c>
-      <c r="J93" s="8">
-        <v>0</v>
-      </c>
-      <c r="K93" s="8">
-        <v>4</v>
-      </c>
-      <c r="L93" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">azs</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F94" s="9">
-        <v>37</v>
-      </c>
-      <c r="G94" s="9">
-        <v>40</v>
-      </c>
-      <c r="H94" s="9">
-        <v>4</v>
-      </c>
-      <c r="I94" s="9">
-        <v>0</v>
-      </c>
-      <c r="J94" s="9">
-        <v>0</v>
-      </c>
-      <c r="K94" s="9">
-        <v>4</v>
-      </c>
-      <c r="L94" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(ブロック外)</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8">
-        <v>10</v>
-      </c>
-      <c r="I95" s="8">
-        <v>7</v>
-      </c>
-      <c r="J95" s="8">
-        <v>3</v>
-      </c>
-      <c r="K95" s="8">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F96" s="9">
-        <v>5</v>
-      </c>
-      <c r="G96" s="9">
-        <v>14</v>
-      </c>
-      <c r="H96" s="9">
-        <v>10</v>
-      </c>
-      <c r="I96" s="9">
-        <v>1</v>
-      </c>
-      <c r="J96" s="9">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9">
-        <v>9</v>
-      </c>
-      <c r="L96" s="9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">locals</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F97" s="8">
-        <v>16</v>
-      </c>
-      <c r="G97" s="8">
-        <v>22</v>
-      </c>
-      <c r="H97" s="8">
-        <v>7</v>
-      </c>
-      <c r="I97" s="8">
-        <v>0</v>
-      </c>
-      <c r="J97" s="8">
-        <v>1</v>
-      </c>
-      <c r="K97" s="8">
-        <v>6</v>
-      </c>
-      <c r="L97" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_vpc</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F98" s="9">
-        <v>24</v>
-      </c>
-      <c r="G98" s="9">
-        <v>33</v>
-      </c>
-      <c r="H98" s="9">
-        <v>10</v>
-      </c>
-      <c r="I98" s="9">
-        <v>1</v>
-      </c>
-      <c r="J98" s="9">
-        <v>1</v>
-      </c>
-      <c r="K98" s="9">
-        <v>8</v>
-      </c>
-      <c r="L98" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resource</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aws_internet_gateway</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F99" s="8">
-        <v>35</v>
-      </c>
-      <c r="G99" s="8">
-        <v>45</v>
-      </c>
-      <c r="H99" s="8">
-        <v>11</v>
-      </c>
-      <c r="I99" s="8">
-        <v>1</v>
-      </c>
-      <c r="J99" s="8">
-        <v>4</v>
-      </c>
-      <c r="K99" s="8">
-        <v>6</v>
-      </c>
-      <c r="L99" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpc_cidr</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F100" s="9">
-        <v>47</v>
-      </c>
-      <c r="G100" s="9">
-        <v>51</v>
-      </c>
-      <c r="H100" s="9">
-        <v>5</v>
-      </c>
-      <c r="I100" s="9">
-        <v>0</v>
-      </c>
-      <c r="J100" s="9">
-        <v>0</v>
-      </c>
-      <c r="K100" s="9">
-        <v>5</v>
-      </c>
-      <c r="L100" s="9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">variable</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env_name</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F101" s="8">
-        <v>53</v>
-      </c>
-      <c r="G101" s="8">
-        <v>55</v>
-      </c>
-      <c r="H101" s="8">
-        <v>3</v>
-      </c>
-      <c r="I101" s="8">
-        <v>0</v>
-      </c>
-      <c r="J101" s="8">
-        <v>0</v>
-      </c>
-      <c r="K101" s="8">
-        <v>3</v>
-      </c>
-      <c r="L101" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pr/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">output</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vpc_id</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F102" s="9">
-        <v>57</v>
-      </c>
-      <c r="G102" s="9">
-        <v>59</v>
-      </c>
-      <c r="H102" s="9">
-        <v>3</v>
-      </c>
-      <c r="I102" s="9">
-        <v>0</v>
-      </c>
-      <c r="J102" s="9">
-        <v>0</v>
-      </c>
-      <c r="K102" s="9">
-        <v>3</v>
-      </c>
-      <c r="L102" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="14" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98 件</t>
-        </is>
-      </c>
-      <c r="C103" s="16"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15">
-        <v>665</v>
-      </c>
-      <c r="I103" s="15">
-        <v>132</v>
-      </c>
-      <c r="J103" s="15">
-        <v>58</v>
-      </c>
-      <c r="K103" s="15">
-        <v>475</v>
-      </c>
-      <c r="L103" s="15">
-        <v>475</v>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63 件</t>
+        </is>
+      </c>
+      <c r="C68" s="16"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15">
+        <v>417</v>
+      </c>
+      <c r="I68" s="15">
+        <v>83</v>
+      </c>
+      <c r="J68" s="15">
+        <v>36</v>
+      </c>
+      <c r="K68" s="15">
+        <v>298</v>
+      </c>
+      <c r="L68" s="15">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L102"/>
+  <autoFilter ref="A4:L67"/>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="L5:L102">
+  <conditionalFormatting sqref="L5:L67">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -7570,8 +5804,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="70" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7593,7 +5827,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一パスのファイルが存在する他環境の実測値から 中央値 で推測しています</t>
+          <t xml:space="preserve">terraform/stacks 配下でファイル数が j1 より少ない環境について、j1 にのみ存在するファイルを j1 の実測値で推測しています</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -7667,7 +5901,7 @@
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/j3/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -7692,12 +5926,12 @@
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">中央値</t>
+          <t xml:space="preserve">j1 の実測値</t>
         </is>
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,st,pr の中央値 (4環境)</t>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
         </is>
       </c>
     </row>
@@ -7709,7 +5943,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/j3/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -7734,12 +5968,12 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">中央値</t>
+          <t xml:space="preserve">j1 の実測値</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,st の中央値 (3環境)</t>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
         </is>
       </c>
     </row>
@@ -7751,7 +5985,7 @@
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/st/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
@@ -7776,24 +6010,24 @@
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">中央値</t>
+          <t xml:space="preserve">j1 の実測値</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,j3,pr の中央値 (4環境)</t>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr</t>
+          <t xml:space="preserve">st</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/st/main.tf</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -7818,94 +6052,220 @@
       </c>
       <c r="I8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">中央値</t>
+          <t xml:space="preserve">j1 の実測値</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,j3,st の中央値 (4環境)</t>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/main.tf)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr</t>
+          <t xml:space="preserve">st</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pr/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/st/network/subnet.tf</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D9" s="19">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E9" s="19">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F9" s="19">
         <v>1</v>
       </c>
       <c r="G9" s="19">
+        <v>30</v>
+      </c>
+      <c r="H9" s="19">
+        <v>30</v>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/subnet.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D10" s="21">
+        <v>59</v>
+      </c>
+      <c r="E10" s="21">
+        <v>10</v>
+      </c>
+      <c r="F10" s="21">
+        <v>9</v>
+      </c>
+      <c r="G10" s="21">
+        <v>40</v>
+      </c>
+      <c r="H10" s="21">
+        <v>40</v>
+      </c>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/vpc.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D11" s="19">
+        <v>17</v>
+      </c>
+      <c r="E11" s="19">
+        <v>4</v>
+      </c>
+      <c r="F11" s="19">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19">
         <v>12</v>
       </c>
-      <c r="H9" s="19">
+      <c r="H11" s="19">
         <v>12</v>
       </c>
-      <c r="I9" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中央値</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1,j2,st の中央値 (3環境)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/st/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D12" s="21">
+        <v>43</v>
+      </c>
+      <c r="E12" s="21">
+        <v>9</v>
+      </c>
+      <c r="F12" s="21">
+        <v>5</v>
+      </c>
+      <c r="G12" s="21">
+        <v>29</v>
+      </c>
+      <c r="H12" s="21">
+        <v>29</v>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/deploy.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 件</t>
-        </is>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15">
-        <v>124</v>
-      </c>
-      <c r="E10" s="15">
-        <v>28</v>
-      </c>
-      <c r="F10" s="15">
-        <v>5</v>
-      </c>
-      <c r="G10" s="15">
-        <v>91</v>
-      </c>
-      <c r="H10" s="15">
-        <v>91</v>
-      </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="14"/>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 件</t>
+        </is>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15">
+        <v>266</v>
+      </c>
+      <c r="E13" s="15">
+        <v>56</v>
+      </c>
+      <c r="F13" s="15">
+        <v>20</v>
+      </c>
+      <c r="G13" s="15">
+        <v>190</v>
+      </c>
+      <c r="H13" s="15">
+        <v>190</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J9"/>
+  <autoFilter ref="A4:J12"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H9">
+  <conditionalFormatting sqref="H5:H12">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/out/step_count.xlsx
+++ b/out/step_count.xlsx
@@ -355,7 +355,7 @@
     <row r="2" ht="16.0" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象: /c/Users/taka_/Claude/Step_Count_Tool/sample    計測日時: 2026-09-23 15:46:02    有効ステップ = 総行数 - 空白行 - コメント行</t>
+          <t xml:space="preserve">対象: /c/Users/taka_/Claude/Step_Count_Tool/sample    計測日時: 2026-09-23 20:28:08    有効ステップ = 総行数 - 空白行 - コメント行</t>
         </is>
       </c>
       <c r="C2" s="2"/>
@@ -420,22 +420,22 @@
     </row>
     <row r="7" ht="34.0" customHeight="1">
       <c r="B7" s="25">
-        <v>616</v>
+        <v>786</v>
       </c>
       <c r="C7" s="25">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25">
-        <v>872</v>
+        <v>1124</v>
       </c>
       <c r="F7" s="25"/>
       <c r="G7" s="25">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H7" s="25"/>
       <c r="I7" s="25">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="0"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 15:46:02</t>
+          <t xml:space="preserve">2026-09-23 20:28:08</t>
         </is>
       </c>
       <c r="D11" s="23"/>
@@ -605,7 +605,7 @@
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">実施 (検出ブロック数: 52)</t>
+          <t xml:space="preserve">実施 (検出ブロック数: 69)</t>
         </is>
       </c>
       <c r="D17" s="23"/>
@@ -625,7 +625,7 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">実施 / 基準環境 terraform/stacks/j1 の実測値 (推測ファイル数: 8)</t>
+          <t xml:space="preserve">実施 / 配置先ごとに基準環境 j1 の実測値 (推測ファイル数: 12)</t>
         </is>
       </c>
       <c r="D18" s="23"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2: 推測なし (6 ファイル / j1: 6 ファイル)    j3: 2 件推測 (4 ファイル / j1: 6 ファイル)    st: 6 件推測 (0 ファイル / j1: 6 ファイル)    pr: ディレクトリなし (推測しない)</t>
+          <t xml:space="preserve">[terraform/stacks/01-workload/env]  j2: 推測なし (6 ファイル / j1: 6 ファイル)    j3: 2 件推測 (4 ファイル / j1: 6 ファイル)    st: 6 件推測 (0 ファイル / j1: 6 ファイル)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D19" s="23"/>
@@ -658,14 +658,10 @@
       <c r="K19" s="23"/>
     </row>
     <row r="20" ht="18.0" customHeight="1">
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測の対象外</t>
-        </is>
-      </c>
+      <c r="B20" s="22"/>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">containers 配下 / terraform/stacks 以外の環境ディレクトリ</t>
+          <t xml:space="preserve">[terraform/stacks/02-apprelease/env]  j2: 推測なし (2 ファイル / j1: 2 ファイル)    j3: ディレクトリなし (推測しない)    st: 1 件推測 (1 ファイル / j1: 2 ファイル)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D20" s="23"/>
@@ -678,14 +674,10 @@
       <c r="K20" s="23"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境ディレクトリ</t>
-        </is>
-      </c>
+      <c r="B21" s="22"/>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">j1,j2,j3,st</t>
+          <t xml:space="preserve">[terraform/stacks/03-dbrelease/env]  j2: 2 件推測 (0 ファイル / j1: 2 ファイル)    j3: ディレクトリなし (推測しない)    st: ディレクトリなし (推測しない)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D21" s="23"/>
@@ -698,14 +690,10 @@
       <c r="K21" s="23"/>
     </row>
     <row r="22" ht="18.0" customHeight="1">
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効ステップ数の定義</t>
-        </is>
-      </c>
+      <c r="B22" s="22"/>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効ステップ = 総行数 - 空白行 - コメント行</t>
+          <t xml:space="preserve">[scripts/cicd/app_release/build_stage]  j2: 1 件推測 (1 ファイル / j1: 2 ファイル)    j3: ディレクトリなし (推測しない)    st: ディレクトリなし (推測しない)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D22" s="23"/>
@@ -718,14 +706,10 @@
       <c r="K22" s="23"/>
     </row>
     <row r="23" ht="18.0" customHeight="1">
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">生成ツール</t>
-        </is>
-      </c>
+      <c r="B23" s="22"/>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">step_count.sh 1.0.0</t>
+          <t xml:space="preserve">[scripts/cicd/app_release/merge_stage]  j2: 推測なし (1 ファイル / j1: 1 ファイル)    j3: ディレクトリなし (推測しない)    st: ディレクトリなし (推測しない)    pr: ディレクトリなし (推測しない)</t>
         </is>
       </c>
       <c r="D23" s="23"/>
@@ -737,588 +721,688 @@
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
     </row>
-    <row r="24" ht="8" customHeight="1"/>
-    <row r="25" ht="26.0" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="24" ht="18.0" customHeight="1">
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測の対象外</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">containers 配下 / 配置先の外にあるファイル</t>
+        </is>
+      </c>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+    </row>
+    <row r="25" ht="18.0" customHeight="1">
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境ディレクトリ</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1,j2,j3,st</t>
+        </is>
+      </c>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+    </row>
+    <row r="26" ht="18.0" customHeight="1">
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境ディレクトリの配置先</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env,terraform/stacks/02-apprelease/env,terraform/stacks/03-dbrelease/env,scripts/cicd/app_release/build_stage,scripts/cicd/app_release/merge_stage</t>
+        </is>
+      </c>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+    </row>
+    <row r="27" ht="18.0" customHeight="1">
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効ステップ数の定義</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効ステップ = 総行数 - 空白行 - コメント行</t>
+        </is>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+    </row>
+    <row r="28" ht="18.0" customHeight="1">
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成ツール</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">step_count.sh 1.0.0</t>
+        </is>
+      </c>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="26.0" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3.  拡張子別 集計</t>
         </is>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" ht="30.0" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" ht="30.0" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">拡張子</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ファイル数</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">総行数</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">空白行数</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コメント行数</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">コード行数</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">有効ステップ数</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">構成比</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ファイル数</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">推測ステップ数</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="C27" s="8">
+      <c r="C32" s="8">
+        <v>18</v>
+      </c>
+      <c r="D32" s="8">
+        <v>350</v>
+      </c>
+      <c r="E32" s="8">
+        <v>77</v>
+      </c>
+      <c r="F32" s="8">
+        <v>46</v>
+      </c>
+      <c r="G32" s="8">
+        <v>227</v>
+      </c>
+      <c r="H32" s="8">
+        <v>227</v>
+      </c>
+      <c r="I32" s="12">
+        <v>0.288804</v>
+      </c>
+      <c r="J32" s="8">
+        <v>4</v>
+      </c>
+      <c r="K32" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="C33" s="9">
+        <v>26</v>
+      </c>
+      <c r="D33" s="9">
+        <v>774</v>
+      </c>
+      <c r="E33" s="9">
+        <v>150</v>
+      </c>
+      <c r="F33" s="9">
+        <v>65</v>
+      </c>
+      <c r="G33" s="9">
+        <v>559</v>
+      </c>
+      <c r="H33" s="9">
+        <v>559</v>
+      </c>
+      <c r="I33" s="13">
+        <v>0.711196</v>
+      </c>
+      <c r="J33" s="9">
+        <v>8</v>
+      </c>
+      <c r="K33" s="9">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" ht="20.0" customHeight="1">
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合計</t>
+        </is>
+      </c>
+      <c r="C34" s="15">
+        <v>44</v>
+      </c>
+      <c r="D34" s="15">
+        <v>1124</v>
+      </c>
+      <c r="E34" s="15">
+        <v>227</v>
+      </c>
+      <c r="F34" s="15">
+        <v>111</v>
+      </c>
+      <c r="G34" s="15">
+        <v>786</v>
+      </c>
+      <c r="H34" s="15">
+        <v>786</v>
+      </c>
+      <c r="I34" s="17">
+        <v>1.000000</v>
+      </c>
+      <c r="J34" s="15">
         <v>12</v>
       </c>
-      <c r="D27" s="8">
-        <v>266</v>
-      </c>
-      <c r="E27" s="8">
-        <v>57</v>
-      </c>
-      <c r="F27" s="8">
-        <v>28</v>
-      </c>
-      <c r="G27" s="8">
-        <v>181</v>
-      </c>
-      <c r="H27" s="8">
-        <v>181</v>
-      </c>
-      <c r="I27" s="12">
-        <v>0.293831</v>
-      </c>
-      <c r="J27" s="8">
-        <v>3</v>
-      </c>
-      <c r="K27" s="8">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="C28" s="9">
-        <v>16</v>
-      </c>
-      <c r="D28" s="9">
-        <v>606</v>
-      </c>
-      <c r="E28" s="9">
-        <v>122</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="K34" s="15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="26.0" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.  環境別 集計</t>
+        </is>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+    </row>
+    <row r="37" ht="30.0" customHeight="1">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ファイル数</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">総行数</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">空白行数</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コメント行数</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コード行数</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効ステップ数</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">構成比</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測ファイル数</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測ステップ数</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1</t>
+        </is>
+      </c>
+      <c r="C38" s="8">
+        <v>15</v>
+      </c>
+      <c r="D38" s="8">
+        <v>331</v>
+      </c>
+      <c r="E38" s="8">
+        <v>67</v>
+      </c>
+      <c r="F38" s="8">
+        <v>36</v>
+      </c>
+      <c r="G38" s="8">
+        <v>228</v>
+      </c>
+      <c r="H38" s="8">
+        <v>228</v>
+      </c>
+      <c r="I38" s="12">
+        <v>0.290076</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0</v>
+      </c>
+      <c r="K38" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="C39" s="9">
+        <v>14</v>
+      </c>
+      <c r="D39" s="9">
+        <v>336</v>
+      </c>
+      <c r="E39" s="9">
+        <v>68</v>
+      </c>
+      <c r="F39" s="9">
+        <v>36</v>
+      </c>
+      <c r="G39" s="9">
+        <v>232</v>
+      </c>
+      <c r="H39" s="9">
+        <v>232</v>
+      </c>
+      <c r="I39" s="13">
+        <v>0.295165</v>
+      </c>
+      <c r="J39" s="9">
+        <v>3</v>
+      </c>
+      <c r="K39" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="C40" s="8">
+        <v>6</v>
+      </c>
+      <c r="D40" s="8">
+        <v>209</v>
+      </c>
+      <c r="E40" s="8">
+        <v>43</v>
+      </c>
+      <c r="F40" s="8">
+        <v>18</v>
+      </c>
+      <c r="G40" s="8">
+        <v>148</v>
+      </c>
+      <c r="H40" s="8">
+        <v>148</v>
+      </c>
+      <c r="I40" s="12">
+        <v>0.188295</v>
+      </c>
+      <c r="J40" s="8">
+        <v>2</v>
+      </c>
+      <c r="K40" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="C41" s="9">
+        <v>8</v>
+      </c>
+      <c r="D41" s="9">
+        <v>245</v>
+      </c>
+      <c r="E41" s="9">
         <v>49</v>
       </c>
-      <c r="G28" s="9">
-        <v>435</v>
-      </c>
-      <c r="H28" s="9">
-        <v>435</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0.706169</v>
-      </c>
-      <c r="J28" s="9">
-        <v>5</v>
-      </c>
-      <c r="K28" s="9">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" ht="20.0" customHeight="1">
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合計</t>
-        </is>
-      </c>
-      <c r="C29" s="15">
-        <v>28</v>
-      </c>
-      <c r="D29" s="15">
-        <v>872</v>
-      </c>
-      <c r="E29" s="15">
-        <v>179</v>
-      </c>
-      <c r="F29" s="15">
-        <v>77</v>
-      </c>
-      <c r="G29" s="15">
-        <v>616</v>
-      </c>
-      <c r="H29" s="15">
-        <v>616</v>
-      </c>
-      <c r="I29" s="17">
-        <v>1.000000</v>
-      </c>
-      <c r="J29" s="15">
-        <v>8</v>
-      </c>
-      <c r="K29" s="15">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="26.0" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.  環境別 集計</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" ht="30.0" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ファイル数</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">総行数</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">空白行数</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コメント行数</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">コード行数</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">有効ステップ数</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">構成比</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測ファイル数</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測ステップ数</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j1</t>
-        </is>
-      </c>
-      <c r="C33" s="8">
-        <v>8</v>
-      </c>
-      <c r="D33" s="8">
-        <v>223</v>
-      </c>
-      <c r="E33" s="8">
-        <v>46</v>
-      </c>
-      <c r="F33" s="8">
+      <c r="F41" s="9">
         <v>20</v>
       </c>
-      <c r="G33" s="8">
-        <v>157</v>
-      </c>
-      <c r="H33" s="8">
-        <v>157</v>
-      </c>
-      <c r="I33" s="12">
-        <v>0.254870</v>
-      </c>
-      <c r="J33" s="8">
-        <v>0</v>
-      </c>
-      <c r="K33" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j2</t>
-        </is>
-      </c>
-      <c r="C34" s="9">
+      <c r="G41" s="9">
+        <v>176</v>
+      </c>
+      <c r="H41" s="9">
+        <v>176</v>
+      </c>
+      <c r="I41" s="13">
+        <v>0.223919</v>
+      </c>
+      <c r="J41" s="9">
         <v>7</v>
       </c>
-      <c r="D34" s="9">
-        <v>228</v>
-      </c>
-      <c r="E34" s="9">
-        <v>47</v>
-      </c>
-      <c r="F34" s="9">
-        <v>20</v>
-      </c>
-      <c r="G34" s="9">
-        <v>161</v>
-      </c>
-      <c r="H34" s="9">
-        <v>161</v>
-      </c>
-      <c r="I34" s="13">
-        <v>0.261364</v>
-      </c>
-      <c r="J34" s="9">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="C35" s="8">
-        <v>6</v>
-      </c>
-      <c r="D35" s="8">
-        <v>209</v>
-      </c>
-      <c r="E35" s="8">
-        <v>43</v>
-      </c>
-      <c r="F35" s="8">
-        <v>18</v>
-      </c>
-      <c r="G35" s="8">
-        <v>148</v>
-      </c>
-      <c r="H35" s="8">
-        <v>148</v>
-      </c>
-      <c r="I35" s="12">
-        <v>0.240260</v>
-      </c>
-      <c r="J35" s="8">
-        <v>2</v>
-      </c>
-      <c r="K35" s="8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="C36" s="9">
-        <v>6</v>
-      </c>
-      <c r="D36" s="9">
-        <v>209</v>
-      </c>
-      <c r="E36" s="9">
-        <v>43</v>
-      </c>
-      <c r="F36" s="9">
-        <v>18</v>
-      </c>
-      <c r="G36" s="9">
-        <v>148</v>
-      </c>
-      <c r="H36" s="9">
-        <v>148</v>
-      </c>
-      <c r="I36" s="13">
-        <v>0.240260</v>
-      </c>
-      <c r="J36" s="9">
-        <v>6</v>
-      </c>
-      <c r="K36" s="9">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(環境ディレクトリ外)</t>
-        </is>
-      </c>
-      <c r="C37" s="8">
-        <v>1</v>
-      </c>
-      <c r="D37" s="8">
-        <v>3</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0</v>
-      </c>
-      <c r="F37" s="8">
-        <v>1</v>
-      </c>
-      <c r="G37" s="8">
-        <v>2</v>
-      </c>
-      <c r="H37" s="8">
-        <v>2</v>
-      </c>
-      <c r="I37" s="12">
-        <v>0.003247</v>
-      </c>
-      <c r="J37" s="8">
-        <v>0</v>
-      </c>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="20.0" customHeight="1">
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合計</t>
-        </is>
-      </c>
-      <c r="C38" s="15">
-        <v>28</v>
-      </c>
-      <c r="D38" s="15">
-        <v>872</v>
-      </c>
-      <c r="E38" s="15">
-        <v>179</v>
-      </c>
-      <c r="F38" s="15">
-        <v>77</v>
-      </c>
-      <c r="G38" s="15">
-        <v>616</v>
-      </c>
-      <c r="H38" s="15">
-        <v>616</v>
-      </c>
-      <c r="I38" s="17">
-        <v>1.000000</v>
-      </c>
-      <c r="J38" s="15">
-        <v>8</v>
-      </c>
-      <c r="K38" s="15">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="26.0" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.  環境 x 拡張子 別 有効ステップ数</t>
-        </is>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">環境</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合計</t>
-        </is>
+      <c r="K41" s="9">
+        <v>166</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">(環境ディレクトリ外)</t>
+        </is>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8">
+        <v>3</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0</v>
+      </c>
+      <c r="F42" s="8">
+        <v>1</v>
+      </c>
+      <c r="G42" s="8">
+        <v>2</v>
+      </c>
+      <c r="H42" s="8">
+        <v>2</v>
+      </c>
+      <c r="I42" s="12">
+        <v>0.002545</v>
+      </c>
+      <c r="J42" s="8">
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="20.0" customHeight="1">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合計</t>
+        </is>
+      </c>
+      <c r="C43" s="15">
+        <v>44</v>
+      </c>
+      <c r="D43" s="15">
+        <v>1124</v>
+      </c>
+      <c r="E43" s="15">
+        <v>227</v>
+      </c>
+      <c r="F43" s="15">
+        <v>111</v>
+      </c>
+      <c r="G43" s="15">
+        <v>786</v>
+      </c>
+      <c r="H43" s="15">
+        <v>786</v>
+      </c>
+      <c r="I43" s="17">
+        <v>1.000000</v>
+      </c>
+      <c r="J43" s="15">
+        <v>12</v>
+      </c>
+      <c r="K43" s="15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="26.0" customHeight="1">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.  環境 x 拡張子 別 有効ステップ数</t>
+        </is>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+    </row>
+    <row r="46" ht="30.0" customHeight="1">
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">環境</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">j1</t>
         </is>
       </c>
-      <c r="C42" s="8">
-        <v>50</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="C47" s="8">
+        <v>73</v>
+      </c>
+      <c r="D47" s="8">
+        <v>155</v>
+      </c>
+      <c r="E47" s="8">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="C48" s="9">
+        <v>70</v>
+      </c>
+      <c r="D48" s="9">
+        <v>162</v>
+      </c>
+      <c r="E48" s="9">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="C49" s="8">
+        <v>41</v>
+      </c>
+      <c r="D49" s="8">
         <v>107</v>
       </c>
-      <c r="E42" s="8">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j2</t>
-        </is>
-      </c>
-      <c r="C43" s="9">
-        <v>47</v>
-      </c>
-      <c r="D43" s="9">
-        <v>114</v>
-      </c>
-      <c r="E43" s="9">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="C44" s="8">
+      <c r="E49" s="8">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="C50" s="9">
         <v>41</v>
       </c>
-      <c r="D44" s="8">
-        <v>107</v>
-      </c>
-      <c r="E44" s="8">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st</t>
-        </is>
-      </c>
-      <c r="C45" s="9">
-        <v>41</v>
-      </c>
-      <c r="D45" s="9">
-        <v>107</v>
-      </c>
-      <c r="E45" s="9">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+      <c r="D50" s="9">
+        <v>135</v>
+      </c>
+      <c r="E50" s="9">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">(環境ディレクトリ外)</t>
         </is>
       </c>
-      <c r="C46" s="8">
+      <c r="C51" s="8">
         <v>2</v>
       </c>
-      <c r="D46" s="8">
-        <v>0</v>
-      </c>
-      <c r="E46" s="8">
+      <c r="D51" s="8">
+        <v>0</v>
+      </c>
+      <c r="E51" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="47" ht="20.0" customHeight="1">
-      <c r="B47" s="14" t="inlineStr">
+    <row r="52" ht="20.0" customHeight="1">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="C47" s="15">
-        <v>181</v>
-      </c>
-      <c r="D47" s="15">
-        <v>435</v>
-      </c>
-      <c r="E47" s="15">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="48" ht="8" customHeight="1"/>
+      <c r="C52" s="15">
+        <v>227</v>
+      </c>
+      <c r="D52" s="15">
+        <v>559</v>
+      </c>
+      <c r="E52" s="15">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="34">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B4:K4"/>
@@ -1345,11 +1429,16 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="C23:K23"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="B31:K31"/>
-    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K28"/>
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="B36:K36"/>
+    <mergeCell ref="B45:K45"/>
   </mergeCells>
-  <conditionalFormatting sqref="H27:H28">
+  <conditionalFormatting sqref="H32:H33">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1358,7 +1447,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H33:H37">
+  <conditionalFormatting sqref="H38:H42">
     <cfRule type="dataBar" priority="2">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1367,7 +1456,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E42:E46">
+  <conditionalFormatting sqref="E47:E51">
     <cfRule type="dataBar" priority="3">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1571,12 +1660,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/build_stage/j1/build.sh</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1585,19 +1674,19 @@
         </is>
       </c>
       <c r="E7" s="8">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F7" s="8">
+        <v>4</v>
+      </c>
+      <c r="G7" s="8">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8">
         <v>9</v>
       </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>30</v>
-      </c>
       <c r="I7" s="8">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1609,12 +1698,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/build_stage/j1/push_image.sh</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1623,13 +1712,13 @@
         </is>
       </c>
       <c r="E8" s="9">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="9">
         <v>7</v>
@@ -1647,12 +1736,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/merge_stage/j1/merge.sh</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -1661,19 +1750,19 @@
         </is>
       </c>
       <c r="E9" s="8">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="F9" s="8">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G9" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I9" s="8">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1685,7 +1774,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1699,19 +1788,19 @@
         </is>
       </c>
       <c r="E10" s="9">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F10" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H10" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J10" s="7"/>
     </row>
@@ -1723,12 +1812,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -1737,19 +1826,19 @@
         </is>
       </c>
       <c r="E11" s="8">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F11" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
       </c>
       <c r="H11" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I11" s="8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -1761,12 +1850,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/scripts/deploy.sh</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1775,36 +1864,36 @@
         </is>
       </c>
       <c r="E12" s="9">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F12" s="9">
         <v>9</v>
       </c>
       <c r="G12" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I12" s="9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J12" s="7"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">containers/j2/app/entrypoint.sh</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -1813,36 +1902,36 @@
         </is>
       </c>
       <c r="E13" s="8">
+        <v>59</v>
+      </c>
+      <c r="F13" s="8">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8">
         <v>9</v>
       </c>
-      <c r="F13" s="8">
-        <v>2</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
       <c r="H13" s="8">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="I13" s="8">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="J13" s="6"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1851,36 +1940,36 @@
         </is>
       </c>
       <c r="E14" s="9">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F14" s="9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
       </c>
       <c r="H14" s="9">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I14" s="9">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/scripts/deploy.sh</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1889,31 +1978,31 @@
         </is>
       </c>
       <c r="E15" s="8">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F15" s="8">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G15" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="8">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I15" s="8">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="J15" s="6"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/ecs/service.tf</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1927,31 +2016,31 @@
         </is>
       </c>
       <c r="E16" s="9">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F16" s="9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
       </c>
       <c r="H16" s="9">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I16" s="9">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J16" s="7"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1965,36 +2054,36 @@
         </is>
       </c>
       <c r="E17" s="8">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F17" s="8">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8">
         <v>10</v>
       </c>
-      <c r="H17" s="8">
-        <v>47</v>
-      </c>
       <c r="I17" s="8">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J17" s="6"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -2003,116 +2092,112 @@
         </is>
       </c>
       <c r="E18" s="9">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F18" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
       </c>
       <c r="H18" s="9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I18" s="9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J18" s="7"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">j1</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E19" s="8">
+        <v>20</v>
+      </c>
+      <c r="F19" s="8">
+        <v>3</v>
+      </c>
+      <c r="G19" s="8">
+        <v>4</v>
+      </c>
+      <c r="H19" s="8">
+        <v>13</v>
+      </c>
+      <c r="I19" s="8">
+        <v>13</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">j2</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j2/scripts/deploy.sh</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">containers/j2/app/entrypoint.sh</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実測</t>
         </is>
       </c>
-      <c r="E19" s="8">
-        <v>43</v>
-      </c>
-      <c r="F19" s="8">
+      <c r="E20" s="9">
         <v>9</v>
       </c>
-      <c r="G19" s="8">
-        <v>5</v>
-      </c>
-      <c r="H19" s="8">
-        <v>29</v>
-      </c>
-      <c r="I19" s="8">
-        <v>29</v>
-      </c>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j3/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測</t>
-        </is>
-      </c>
-      <c r="E20" s="21">
-        <v>40</v>
-      </c>
-      <c r="F20" s="21">
-        <v>9</v>
-      </c>
-      <c r="G20" s="21">
+      <c r="F20" s="9">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9">
         <v>1</v>
       </c>
-      <c r="H20" s="21">
-        <v>30</v>
-      </c>
-      <c r="I20" s="21">
-        <v>30</v>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
-        </is>
-      </c>
+      <c r="H20" s="9">
+        <v>6</v>
+      </c>
+      <c r="I20" s="9">
+        <v>6</v>
+      </c>
+      <c r="J20" s="7"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/build_stage/j2/build.sh</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -2121,505 +2206,1133 @@
         </is>
       </c>
       <c r="E21" s="8">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F21" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="8">
+        <v>9</v>
+      </c>
+      <c r="I21" s="8">
+        <v>9</v>
+      </c>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scripts/cicd/app_release/build_stage/j2/push_image.sh</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E22" s="21">
+        <v>14</v>
+      </c>
+      <c r="F22" s="21">
+        <v>4</v>
+      </c>
+      <c r="G22" s="21">
+        <v>3</v>
+      </c>
+      <c r="H22" s="21">
         <v>7</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I22" s="21">
         <v>7</v>
       </c>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tf</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">実測</t>
-        </is>
-      </c>
-      <c r="E22" s="9">
-        <v>40</v>
-      </c>
-      <c r="F22" s="9">
-        <v>9</v>
-      </c>
-      <c r="G22" s="9">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9">
-        <v>30</v>
-      </c>
-      <c r="I22" s="9">
-        <v>30</v>
-      </c>
-      <c r="J22" s="7"/>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2 のファイル数 1 &lt; j1 のファイル数 2 (参照: scripts/cicd/app_release/build_stage/j1/push_image.sh)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/merge_stage/j2/merge.sh</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E23" s="8">
+        <v>12</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+      <c r="G23" s="8">
+        <v>3</v>
+      </c>
+      <c r="H23" s="8">
+        <v>7</v>
+      </c>
+      <c r="I23" s="8">
+        <v>7</v>
+      </c>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実測</t>
         </is>
       </c>
-      <c r="E23" s="8">
-        <v>59</v>
-      </c>
-      <c r="F23" s="8">
-        <v>10</v>
-      </c>
-      <c r="G23" s="8">
+      <c r="E24" s="9">
+        <v>40</v>
+      </c>
+      <c r="F24" s="9">
         <v>9</v>
       </c>
-      <c r="H23" s="8">
-        <v>40</v>
-      </c>
-      <c r="I23" s="8">
-        <v>40</v>
-      </c>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j3/scripts/backup.sh</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sh</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">推測</t>
-        </is>
-      </c>
-      <c r="E24" s="21">
-        <v>17</v>
-      </c>
-      <c r="F24" s="21">
-        <v>4</v>
-      </c>
-      <c r="G24" s="21">
+      <c r="G24" s="9">
         <v>1</v>
       </c>
-      <c r="H24" s="21">
-        <v>12</v>
-      </c>
-      <c r="I24" s="21">
-        <v>12</v>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
-        </is>
-      </c>
+      <c r="H24" s="9">
+        <v>30</v>
+      </c>
+      <c r="I24" s="9">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E25" s="8">
+        <v>10</v>
+      </c>
+      <c r="F25" s="8">
+        <v>2</v>
+      </c>
+      <c r="G25" s="8">
+        <v>1</v>
+      </c>
+      <c r="H25" s="8">
+        <v>7</v>
+      </c>
+      <c r="I25" s="8">
+        <v>7</v>
+      </c>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E26" s="9">
+        <v>40</v>
+      </c>
+      <c r="F26" s="9">
+        <v>9</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
+      <c r="H26" s="9">
+        <v>30</v>
+      </c>
+      <c r="I26" s="9">
+        <v>30</v>
+      </c>
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E27" s="8">
+        <v>69</v>
+      </c>
+      <c r="F27" s="8">
+        <v>12</v>
+      </c>
+      <c r="G27" s="8">
+        <v>10</v>
+      </c>
+      <c r="H27" s="8">
+        <v>47</v>
+      </c>
+      <c r="I27" s="8">
+        <v>47</v>
+      </c>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E28" s="9">
+        <v>17</v>
+      </c>
+      <c r="F28" s="9">
+        <v>4</v>
+      </c>
+      <c r="G28" s="9">
+        <v>1</v>
+      </c>
+      <c r="H28" s="9">
+        <v>12</v>
+      </c>
+      <c r="I28" s="9">
+        <v>12</v>
+      </c>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E29" s="8">
+        <v>43</v>
+      </c>
+      <c r="F29" s="8">
+        <v>9</v>
+      </c>
+      <c r="G29" s="8">
+        <v>5</v>
+      </c>
+      <c r="H29" s="8">
+        <v>29</v>
+      </c>
+      <c r="I29" s="8">
+        <v>29</v>
+      </c>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/ecs/service.tf</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E30" s="9">
+        <v>22</v>
+      </c>
+      <c r="F30" s="9">
+        <v>3</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1</v>
+      </c>
+      <c r="H30" s="9">
+        <v>18</v>
+      </c>
+      <c r="I30" s="9">
+        <v>18</v>
+      </c>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E31" s="8">
+        <v>14</v>
+      </c>
+      <c r="F31" s="8">
+        <v>3</v>
+      </c>
+      <c r="G31" s="8">
+        <v>1</v>
+      </c>
+      <c r="H31" s="8">
+        <v>10</v>
+      </c>
+      <c r="I31" s="8">
+        <v>10</v>
+      </c>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E32" s="21">
+        <v>10</v>
+      </c>
+      <c r="F32" s="21">
+        <v>2</v>
+      </c>
+      <c r="G32" s="21">
+        <v>1</v>
+      </c>
+      <c r="H32" s="21">
+        <v>7</v>
+      </c>
+      <c r="I32" s="21">
+        <v>7</v>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2 のファイル数 0 &lt; j1 のファイル数 2 (参照: terraform/stacks/03-dbrelease/env/j1/main.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j2/rds/cluster.tf</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E33" s="19">
+        <v>20</v>
+      </c>
+      <c r="F33" s="19">
+        <v>3</v>
+      </c>
+      <c r="G33" s="19">
+        <v>4</v>
+      </c>
+      <c r="H33" s="19">
+        <v>13</v>
+      </c>
+      <c r="I33" s="19">
+        <v>13</v>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2 のファイル数 0 &lt; j1 のファイル数 2 (参照: terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
           <t xml:space="preserve">j3</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j3/scripts/deploy.sh</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/compute/ec2.tf</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E34" s="21">
+        <v>40</v>
+      </c>
+      <c r="F34" s="21">
+        <v>9</v>
+      </c>
+      <c r="G34" s="21">
+        <v>1</v>
+      </c>
+      <c r="H34" s="21">
+        <v>30</v>
+      </c>
+      <c r="I34" s="21">
+        <v>30</v>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/compute/ec2.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/main.tf</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E35" s="8">
+        <v>10</v>
+      </c>
+      <c r="F35" s="8">
+        <v>2</v>
+      </c>
+      <c r="G35" s="8">
+        <v>1</v>
+      </c>
+      <c r="H35" s="8">
+        <v>7</v>
+      </c>
+      <c r="I35" s="8">
+        <v>7</v>
+      </c>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E36" s="9">
+        <v>40</v>
+      </c>
+      <c r="F36" s="9">
+        <v>9</v>
+      </c>
+      <c r="G36" s="9">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9">
+        <v>30</v>
+      </c>
+      <c r="I36" s="9">
+        <v>30</v>
+      </c>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E37" s="8">
+        <v>59</v>
+      </c>
+      <c r="F37" s="8">
+        <v>10</v>
+      </c>
+      <c r="G37" s="8">
+        <v>9</v>
+      </c>
+      <c r="H37" s="8">
+        <v>40</v>
+      </c>
+      <c r="I37" s="8">
+        <v>40</v>
+      </c>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E38" s="21">
+        <v>17</v>
+      </c>
+      <c r="F38" s="21">
+        <v>4</v>
+      </c>
+      <c r="G38" s="21">
+        <v>1</v>
+      </c>
+      <c r="H38" s="21">
+        <v>12</v>
+      </c>
+      <c r="I38" s="21">
+        <v>12</v>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/backup.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">実測</t>
         </is>
       </c>
-      <c r="E25" s="8">
+      <c r="E39" s="8">
         <v>43</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F39" s="8">
         <v>9</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G39" s="8">
         <v>5</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H39" s="8">
         <v>29</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I39" s="8">
         <v>29</v>
       </c>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/compute/ec2.tf</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/compute/ec2.tf</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E40" s="21">
         <v>40</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F40" s="21">
         <v>9</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G40" s="21">
         <v>1</v>
       </c>
-      <c r="H26" s="21">
+      <c r="H40" s="21">
         <v>30</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I40" s="21">
         <v>30</v>
       </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="J40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/compute/ec2.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/main.tf</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E27" s="19">
+      <c r="E41" s="19">
         <v>10</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F41" s="19">
         <v>2</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G41" s="19">
         <v>1</v>
       </c>
-      <c r="H27" s="19">
+      <c r="H41" s="19">
         <v>7</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I41" s="19">
         <v>7</v>
       </c>
-      <c r="J27" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/main.tf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="J41" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/main.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/network/subnet.tf</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E42" s="21">
         <v>40</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F42" s="21">
         <v>9</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G42" s="21">
         <v>1</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H42" s="21">
         <v>30</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I42" s="21">
         <v>30</v>
       </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/subnet.tf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/network/subnet.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">tf</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E29" s="19">
+      <c r="E43" s="19">
         <v>59</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F43" s="19">
         <v>10</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G43" s="19">
         <v>9</v>
       </c>
-      <c r="H29" s="19">
+      <c r="H43" s="19">
         <v>40</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I43" s="19">
         <v>40</v>
       </c>
-      <c r="J29" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/vpc.tf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/network/vpc.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/scripts/backup.sh</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E44" s="21">
         <v>17</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F44" s="21">
         <v>4</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G44" s="21">
         <v>1</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H44" s="21">
         <v>12</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I44" s="21">
         <v>12</v>
       </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="J44" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/backup.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">st</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/st/scripts/deploy.sh</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">推測</t>
         </is>
       </c>
-      <c r="E31" s="19">
+      <c r="E45" s="19">
         <v>43</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F45" s="19">
         <v>9</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G45" s="19">
         <v>5</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H45" s="19">
         <v>29</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I45" s="19">
         <v>29</v>
       </c>
-      <c r="J31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/deploy.sh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/deploy.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/ecs/service.tf</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推測</t>
+        </is>
+      </c>
+      <c r="E46" s="21">
+        <v>22</v>
+      </c>
+      <c r="F46" s="21">
+        <v>3</v>
+      </c>
+      <c r="G46" s="21">
+        <v>1</v>
+      </c>
+      <c r="H46" s="21">
+        <v>18</v>
+      </c>
+      <c r="I46" s="21">
+        <v>18</v>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 1 &lt; j1 のファイル数 2 (参照: terraform/stacks/02-apprelease/env/j1/ecs/service.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実測</t>
+        </is>
+      </c>
+      <c r="E47" s="8">
+        <v>14</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
+      <c r="G47" s="8">
+        <v>1</v>
+      </c>
+      <c r="H47" s="8">
+        <v>10</v>
+      </c>
+      <c r="I47" s="8">
+        <v>10</v>
+      </c>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">(環境外)</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">common/README.sh</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">sh</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">実測</t>
         </is>
       </c>
-      <c r="E32" s="9">
-        <v>3</v>
-      </c>
-      <c r="F32" s="9">
-        <v>0</v>
-      </c>
-      <c r="G32" s="9">
+      <c r="E48" s="9">
+        <v>3</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
         <v>1</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H48" s="9">
         <v>2</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I48" s="9">
         <v>2</v>
       </c>
-      <c r="J32" s="7"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="J48" s="7"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28 件</t>
-        </is>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="15">
-        <v>872</v>
-      </c>
-      <c r="F33" s="15">
-        <v>179</v>
-      </c>
-      <c r="G33" s="15">
-        <v>77</v>
-      </c>
-      <c r="H33" s="15">
-        <v>616</v>
-      </c>
-      <c r="I33" s="15">
-        <v>616</v>
-      </c>
-      <c r="J33" s="14"/>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44 件</t>
+        </is>
+      </c>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="15">
+        <v>1124</v>
+      </c>
+      <c r="F49" s="15">
+        <v>227</v>
+      </c>
+      <c r="G49" s="15">
+        <v>111</v>
+      </c>
+      <c r="H49" s="15">
+        <v>786</v>
+      </c>
+      <c r="I49" s="15">
+        <v>786</v>
+      </c>
+      <c r="J49" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J32"/>
+  <autoFilter ref="A4:J48"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I32">
+  <conditionalFormatting sqref="I5:I48">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -2763,7 +3476,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -2807,7 +3520,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -2855,7 +3568,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2903,7 +3616,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -2951,7 +3664,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -2999,7 +3712,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -3043,7 +3756,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -3091,7 +3804,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -3139,7 +3852,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -3183,7 +3896,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -3231,7 +3944,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -3279,7 +3992,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -3327,7 +4040,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -3375,7 +4088,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/subnet.tf</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -3423,7 +4136,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -3467,7 +4180,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -3515,7 +4228,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -3563,7 +4276,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -3611,7 +4324,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -3659,7 +4372,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -3707,7 +4420,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3755,7 +4468,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j1/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j1/network/vpc.tf</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -3798,12 +4511,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/ecs/service.tf</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -3824,10 +4537,10 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="8">
         <v>1</v>
@@ -3842,37 +4555,37 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/ecs/service.tf</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">data</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_ami</t>
+          <t xml:space="preserve">aws_ecs_task_definition</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">amazon_linux</t>
+          <t xml:space="preserve">app</t>
         </is>
       </c>
       <c r="F28" s="9">
         <v>3</v>
       </c>
       <c r="G28" s="9">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H28" s="9">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I28" s="9">
         <v>1</v>
@@ -3881,21 +4594,21 @@
         <v>0</v>
       </c>
       <c r="K28" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L28" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/ecs/service.tf</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3905,7 +4618,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_instance</t>
+          <t xml:space="preserve">aws_ecs_service</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -3914,46 +4627,46 @@
         </is>
       </c>
       <c r="F29" s="8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G29" s="8">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H29" s="8">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I29" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" s="8">
         <v>0</v>
       </c>
       <c r="K29" s="8">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L29" s="8">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">module</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">alb</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -3961,47 +4674,43 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F30" s="9">
-        <v>30</v>
-      </c>
-      <c r="G30" s="9">
-        <v>35</v>
-      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
       <c r="H30" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I30" s="9">
+        <v>3</v>
+      </c>
+      <c r="J30" s="9">
         <v>1</v>
       </c>
-      <c r="J30" s="9">
-        <v>0</v>
-      </c>
       <c r="K30" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">provider</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">instance_type</t>
+          <t xml:space="preserve">aws</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -4010,13 +4719,13 @@
         </is>
       </c>
       <c r="F31" s="8">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G31" s="8">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H31" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31" s="8">
         <v>0</v>
@@ -4025,31 +4734,31 @@
         <v>0</v>
       </c>
       <c r="K31" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L31" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ブロック外)</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -4057,43 +4766,47 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="9">
+        <v>7</v>
+      </c>
+      <c r="G32" s="9">
+        <v>10</v>
+      </c>
       <c r="H32" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws</t>
+          <t xml:space="preserve">image_tag</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -4102,10 +4815,10 @@
         </is>
       </c>
       <c r="F33" s="8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G33" s="8">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H33" s="8">
         <v>3</v>
@@ -4126,22 +4839,22 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -4149,47 +4862,43 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F34" s="9">
-        <v>7</v>
-      </c>
-      <c r="G34" s="9">
-        <v>10</v>
-      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
       <c r="H34" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ブロック外)</t>
+          <t xml:space="preserve">provider</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">aws</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -4197,202 +4906,202 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
+      <c r="G35" s="8">
+        <v>5</v>
+      </c>
       <c r="H35" s="8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I35" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J35" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/main.tf</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_subnet</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">public</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F36" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G36" s="9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H36" s="9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I36" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9">
         <v>0</v>
       </c>
       <c r="K36" s="9">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L36" s="9">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_subnet</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">private</t>
-        </is>
-      </c>
-      <c r="F37" s="8">
-        <v>15</v>
-      </c>
-      <c r="G37" s="8">
-        <v>25</v>
-      </c>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
       <c r="H37" s="8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I37" s="8">
         <v>2</v>
       </c>
       <c r="J37" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L37" s="8">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">public_subnets</t>
+          <t xml:space="preserve">aws_rds_cluster</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="F38" s="9">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G38" s="9">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H38" s="9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I38" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L38" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j2</t>
+          <t xml:space="preserve">j1</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">private_subnets</t>
+          <t xml:space="preserve">aws_rds_cluster_instance</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="F39" s="8">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G39" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H39" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I39" s="8">
         <v>0</v>
@@ -4401,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="K39" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L39" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -4415,17 +5124,17 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">azs</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -4433,26 +5142,22 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F40" s="9">
-        <v>37</v>
-      </c>
-      <c r="G40" s="9">
-        <v>40</v>
-      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
       <c r="H40" s="9">
+        <v>5</v>
+      </c>
+      <c r="I40" s="9">
         <v>4</v>
       </c>
-      <c r="I40" s="9">
-        <v>0</v>
-      </c>
       <c r="J40" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4463,40 +5168,44 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ブロック外)</t>
+          <t xml:space="preserve">data</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">aws_ami</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+          <t xml:space="preserve">amazon_linux</t>
+        </is>
+      </c>
+      <c r="F41" s="8">
+        <v>3</v>
+      </c>
+      <c r="G41" s="8">
+        <v>11</v>
+      </c>
       <c r="H41" s="8">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I41" s="8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J41" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K41" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" s="8">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -4507,44 +5216,44 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">aws_instance</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">app</t>
         </is>
       </c>
       <c r="F42" s="9">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G42" s="9">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H42" s="9">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I42" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" s="9">
         <v>0</v>
       </c>
       <c r="K42" s="9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L42" s="9">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -4555,17 +5264,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">locals</t>
+          <t xml:space="preserve">module</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">alb</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -4574,25 +5283,25 @@
         </is>
       </c>
       <c r="F43" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G43" s="8">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H43" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I43" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L43" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -4603,44 +5312,44 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_vpc</t>
+          <t xml:space="preserve">instance_type</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">main</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F44" s="9">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G44" s="9">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H44" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L44" s="9">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -4651,44 +5360,40 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/main.tf</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_internet_gateway</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F45" s="8">
-        <v>35</v>
-      </c>
-      <c r="G45" s="8">
-        <v>45</v>
-      </c>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
       <c r="H45" s="8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I45" s="8">
+        <v>2</v>
+      </c>
+      <c r="J45" s="8">
         <v>1</v>
       </c>
-      <c r="J45" s="8">
-        <v>4</v>
-      </c>
       <c r="K45" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L45" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4699,17 +5404,17 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/main.tf</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">provider</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpc_cidr</t>
+          <t xml:space="preserve">aws</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -4718,13 +5423,13 @@
         </is>
       </c>
       <c r="F46" s="9">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="G46" s="9">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="H46" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I46" s="9">
         <v>0</v>
@@ -4733,10 +5438,10 @@
         <v>0</v>
       </c>
       <c r="K46" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L46" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -4747,7 +5452,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/main.tf</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -4757,7 +5462,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">env_name</t>
+          <t xml:space="preserve">region</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -4766,13 +5471,13 @@
         </is>
       </c>
       <c r="F47" s="8">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="G47" s="8">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H47" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="8">
         <v>0</v>
@@ -4781,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="K47" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L47" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -4795,17 +5500,17 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">output</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpc_id</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -4813,26 +5518,22 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F48" s="9">
-        <v>57</v>
-      </c>
-      <c r="G48" s="9">
-        <v>59</v>
-      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
       <c r="H48" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I48" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J48" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4843,7 +5544,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -4853,34 +5554,34 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_nat_gateway</t>
+          <t xml:space="preserve">aws_subnet</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">main</t>
+          <t xml:space="preserve">public</t>
         </is>
       </c>
       <c r="F49" s="8">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="G49" s="8">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="H49" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I49" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L49" s="8">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -4891,7 +5592,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j2/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -4901,55 +5602,55 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_eip</t>
+          <t xml:space="preserve">aws_subnet</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">nat</t>
+          <t xml:space="preserve">private</t>
         </is>
       </c>
       <c r="F50" s="9">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="G50" s="9">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="H50" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I50" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="9">
         <v>0</v>
       </c>
       <c r="K50" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L50" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ブロック外)</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">public_subnets</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4957,43 +5658,47 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
+      <c r="F51" s="8">
+        <v>27</v>
+      </c>
+      <c r="G51" s="8">
+        <v>30</v>
+      </c>
       <c r="H51" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws</t>
+          <t xml:space="preserve">private_subnets</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -5002,13 +5707,13 @@
         </is>
       </c>
       <c r="F52" s="9">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G52" s="9">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H52" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="9">
         <v>0</v>
@@ -5017,21 +5722,21 @@
         <v>0</v>
       </c>
       <c r="K52" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/subnet.tf</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -5041,7 +5746,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">region</t>
+          <t xml:space="preserve">azs</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -5050,10 +5755,10 @@
         </is>
       </c>
       <c r="F53" s="8">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G53" s="8">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H53" s="8">
         <v>4</v>
@@ -5074,12 +5779,12 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
@@ -5100,13 +5805,13 @@
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I54" s="9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J54" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K54" s="9">
         <v>0</v>
@@ -5118,40 +5823,40 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">terraform</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_subnet</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">public</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F55" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" s="8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I55" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" s="8">
         <v>0</v>
@@ -5166,156 +5871,156 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">locals</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_subnet</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">private</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F56" s="9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G56" s="9">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H56" s="9">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I56" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L56" s="9">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">public_subnets</t>
+          <t xml:space="preserve">aws_vpc</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="F57" s="8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G57" s="8">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H57" s="8">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I57" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L57" s="8">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">private_subnets</t>
+          <t xml:space="preserve">aws_internet_gateway</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="F58" s="9">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G58" s="9">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H58" s="9">
+        <v>11</v>
+      </c>
+      <c r="I58" s="9">
+        <v>1</v>
+      </c>
+      <c r="J58" s="9">
         <v>4</v>
       </c>
-      <c r="I58" s="9">
-        <v>0</v>
-      </c>
-      <c r="J58" s="9">
-        <v>0</v>
-      </c>
       <c r="K58" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L58" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -5325,7 +6030,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">azs</t>
+          <t xml:space="preserve">vpc_cidr</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -5334,13 +6039,13 @@
         </is>
       </c>
       <c r="F59" s="8">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G59" s="8">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H59" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="8">
         <v>0</v>
@@ -5349,31 +6054,31 @@
         <v>0</v>
       </c>
       <c r="K59" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L59" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ブロック外)</t>
+          <t xml:space="preserve">variable</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">env_name</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -5381,43 +6086,47 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
+      <c r="F60" s="9">
+        <v>53</v>
+      </c>
+      <c r="G60" s="9">
+        <v>55</v>
+      </c>
       <c r="H60" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I60" s="9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K60" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform</t>
+          <t xml:space="preserve">output</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">vpc_id</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -5426,61 +6135,61 @@
         </is>
       </c>
       <c r="F61" s="8">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G61" s="8">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H61" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I61" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="8">
         <v>0</v>
       </c>
       <c r="K61" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L61" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">locals</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">aws_nat_gateway</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">main</t>
         </is>
       </c>
       <c r="F62" s="9">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="G62" s="9">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="H62" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I62" s="9">
         <v>0</v>
@@ -5489,21 +6198,21 @@
         <v>1</v>
       </c>
       <c r="K62" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L62" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j2/network/vpc.tf</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -5513,166 +6222,162 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_vpc</t>
+          <t xml:space="preserve">aws_eip</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">main</t>
+          <t xml:space="preserve">nat</t>
         </is>
       </c>
       <c r="F63" s="8">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G63" s="8">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="H63" s="8">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I63" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L63" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/ecs/service.tf</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">resource</t>
+          <t xml:space="preserve">(ブロック外)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aws_internet_gateway</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">main</t>
-        </is>
-      </c>
-      <c r="F64" s="9">
-        <v>35</v>
-      </c>
-      <c r="G64" s="9">
-        <v>45</v>
-      </c>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
       <c r="H64" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I64" s="9">
+        <v>2</v>
+      </c>
+      <c r="J64" s="9">
         <v>1</v>
       </c>
-      <c r="J64" s="9">
-        <v>4</v>
-      </c>
       <c r="K64" s="9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/ecs/service.tf</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">vpc_cidr</t>
+          <t xml:space="preserve">aws_ecs_task_definition</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">app</t>
         </is>
       </c>
       <c r="F65" s="8">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="G65" s="8">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="H65" s="8">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I65" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="8">
         <v>0</v>
       </c>
       <c r="K65" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L65" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/ecs/service.tf</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">variable</t>
+          <t xml:space="preserve">resource</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">env_name</t>
+          <t xml:space="preserve">aws_ecs_service</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">app</t>
         </is>
       </c>
       <c r="F66" s="9">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G66" s="9">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="H66" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I66" s="9">
         <v>0</v>
@@ -5681,99 +6386,1231 @@
         <v>0</v>
       </c>
       <c r="K66" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L66" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ブロック外)</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8">
+        <v>4</v>
+      </c>
+      <c r="I67" s="8">
+        <v>3</v>
+      </c>
+      <c r="J67" s="8">
+        <v>1</v>
+      </c>
+      <c r="K67" s="8">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F68" s="9">
+        <v>3</v>
+      </c>
+      <c r="G68" s="9">
+        <v>5</v>
+      </c>
+      <c r="H68" s="9">
+        <v>3</v>
+      </c>
+      <c r="I68" s="9">
+        <v>0</v>
+      </c>
+      <c r="J68" s="9">
+        <v>0</v>
+      </c>
+      <c r="K68" s="9">
+        <v>3</v>
+      </c>
+      <c r="L68" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F69" s="8">
+        <v>7</v>
+      </c>
+      <c r="G69" s="8">
+        <v>10</v>
+      </c>
+      <c r="H69" s="8">
+        <v>4</v>
+      </c>
+      <c r="I69" s="8">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8">
+        <v>0</v>
+      </c>
+      <c r="K69" s="8">
+        <v>4</v>
+      </c>
+      <c r="L69" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j2</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/j2/main.tf</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image_tag</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F70" s="9">
+        <v>12</v>
+      </c>
+      <c r="G70" s="9">
+        <v>14</v>
+      </c>
+      <c r="H70" s="9">
+        <v>3</v>
+      </c>
+      <c r="I70" s="9">
+        <v>0</v>
+      </c>
+      <c r="J70" s="9">
+        <v>0</v>
+      </c>
+      <c r="K70" s="9">
+        <v>3</v>
+      </c>
+      <c r="L70" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">j3</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">terraform/stacks/j3/network/vpc.tf</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/main.tf</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ブロック外)</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8">
+        <v>3</v>
+      </c>
+      <c r="I71" s="8">
+        <v>2</v>
+      </c>
+      <c r="J71" s="8">
+        <v>1</v>
+      </c>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="L71" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/main.tf</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F72" s="9">
+        <v>3</v>
+      </c>
+      <c r="G72" s="9">
+        <v>5</v>
+      </c>
+      <c r="H72" s="9">
+        <v>3</v>
+      </c>
+      <c r="I72" s="9">
+        <v>0</v>
+      </c>
+      <c r="J72" s="9">
+        <v>0</v>
+      </c>
+      <c r="K72" s="9">
+        <v>3</v>
+      </c>
+      <c r="L72" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/main.tf</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F73" s="8">
+        <v>7</v>
+      </c>
+      <c r="G73" s="8">
+        <v>10</v>
+      </c>
+      <c r="H73" s="8">
+        <v>4</v>
+      </c>
+      <c r="I73" s="8">
+        <v>0</v>
+      </c>
+      <c r="J73" s="8">
+        <v>0</v>
+      </c>
+      <c r="K73" s="8">
+        <v>4</v>
+      </c>
+      <c r="L73" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ブロック外)</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9">
+        <v>6</v>
+      </c>
+      <c r="I74" s="9">
+        <v>5</v>
+      </c>
+      <c r="J74" s="9">
+        <v>1</v>
+      </c>
+      <c r="K74" s="9">
+        <v>0</v>
+      </c>
+      <c r="L74" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resource</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws_subnet</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">public</t>
+        </is>
+      </c>
+      <c r="F75" s="8">
+        <v>3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>13</v>
+      </c>
+      <c r="H75" s="8">
+        <v>11</v>
+      </c>
+      <c r="I75" s="8">
+        <v>2</v>
+      </c>
+      <c r="J75" s="8">
+        <v>0</v>
+      </c>
+      <c r="K75" s="8">
+        <v>9</v>
+      </c>
+      <c r="L75" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resource</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws_subnet</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">private</t>
+        </is>
+      </c>
+      <c r="F76" s="9">
+        <v>15</v>
+      </c>
+      <c r="G76" s="9">
+        <v>25</v>
+      </c>
+      <c r="H76" s="9">
+        <v>11</v>
+      </c>
+      <c r="I76" s="9">
+        <v>2</v>
+      </c>
+      <c r="J76" s="9">
+        <v>0</v>
+      </c>
+      <c r="K76" s="9">
+        <v>9</v>
+      </c>
+      <c r="L76" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">public_subnets</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F77" s="8">
+        <v>27</v>
+      </c>
+      <c r="G77" s="8">
+        <v>30</v>
+      </c>
+      <c r="H77" s="8">
+        <v>4</v>
+      </c>
+      <c r="I77" s="8">
+        <v>0</v>
+      </c>
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+      <c r="K77" s="8">
+        <v>4</v>
+      </c>
+      <c r="L77" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">private_subnets</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F78" s="9">
+        <v>32</v>
+      </c>
+      <c r="G78" s="9">
+        <v>35</v>
+      </c>
+      <c r="H78" s="9">
+        <v>4</v>
+      </c>
+      <c r="I78" s="9">
+        <v>0</v>
+      </c>
+      <c r="J78" s="9">
+        <v>0</v>
+      </c>
+      <c r="K78" s="9">
+        <v>4</v>
+      </c>
+      <c r="L78" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/subnet.tf</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azs</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F79" s="8">
+        <v>37</v>
+      </c>
+      <c r="G79" s="8">
+        <v>40</v>
+      </c>
+      <c r="H79" s="8">
+        <v>4</v>
+      </c>
+      <c r="I79" s="8">
+        <v>0</v>
+      </c>
+      <c r="J79" s="8">
+        <v>0</v>
+      </c>
+      <c r="K79" s="8">
+        <v>4</v>
+      </c>
+      <c r="L79" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ブロック外)</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9">
+        <v>10</v>
+      </c>
+      <c r="I80" s="9">
+        <v>7</v>
+      </c>
+      <c r="J80" s="9">
+        <v>3</v>
+      </c>
+      <c r="K80" s="9">
+        <v>0</v>
+      </c>
+      <c r="L80" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F81" s="8">
+        <v>5</v>
+      </c>
+      <c r="G81" s="8">
+        <v>14</v>
+      </c>
+      <c r="H81" s="8">
+        <v>10</v>
+      </c>
+      <c r="I81" s="8">
+        <v>1</v>
+      </c>
+      <c r="J81" s="8">
+        <v>0</v>
+      </c>
+      <c r="K81" s="8">
+        <v>9</v>
+      </c>
+      <c r="L81" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">locals</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F82" s="9">
+        <v>16</v>
+      </c>
+      <c r="G82" s="9">
+        <v>22</v>
+      </c>
+      <c r="H82" s="9">
+        <v>7</v>
+      </c>
+      <c r="I82" s="9">
+        <v>0</v>
+      </c>
+      <c r="J82" s="9">
+        <v>1</v>
+      </c>
+      <c r="K82" s="9">
+        <v>6</v>
+      </c>
+      <c r="L82" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resource</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws_vpc</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">main</t>
+        </is>
+      </c>
+      <c r="F83" s="8">
+        <v>24</v>
+      </c>
+      <c r="G83" s="8">
+        <v>33</v>
+      </c>
+      <c r="H83" s="8">
+        <v>10</v>
+      </c>
+      <c r="I83" s="8">
+        <v>1</v>
+      </c>
+      <c r="J83" s="8">
+        <v>1</v>
+      </c>
+      <c r="K83" s="8">
+        <v>8</v>
+      </c>
+      <c r="L83" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resource</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws_internet_gateway</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">main</t>
+        </is>
+      </c>
+      <c r="F84" s="9">
+        <v>35</v>
+      </c>
+      <c r="G84" s="9">
+        <v>45</v>
+      </c>
+      <c r="H84" s="9">
+        <v>11</v>
+      </c>
+      <c r="I84" s="9">
+        <v>1</v>
+      </c>
+      <c r="J84" s="9">
+        <v>4</v>
+      </c>
+      <c r="K84" s="9">
+        <v>6</v>
+      </c>
+      <c r="L84" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vpc_cidr</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F85" s="8">
+        <v>47</v>
+      </c>
+      <c r="G85" s="8">
+        <v>51</v>
+      </c>
+      <c r="H85" s="8">
+        <v>5</v>
+      </c>
+      <c r="I85" s="8">
+        <v>0</v>
+      </c>
+      <c r="J85" s="8">
+        <v>0</v>
+      </c>
+      <c r="K85" s="8">
+        <v>5</v>
+      </c>
+      <c r="L85" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env_name</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F86" s="9">
+        <v>53</v>
+      </c>
+      <c r="G86" s="9">
+        <v>55</v>
+      </c>
+      <c r="H86" s="9">
+        <v>3</v>
+      </c>
+      <c r="I86" s="9">
+        <v>0</v>
+      </c>
+      <c r="J86" s="9">
+        <v>0</v>
+      </c>
+      <c r="K86" s="9">
+        <v>3</v>
+      </c>
+      <c r="L86" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j3</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">output</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">vpc_id</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F67" s="8">
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F87" s="8">
         <v>57</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G87" s="8">
         <v>59</v>
       </c>
-      <c r="H67" s="8">
-        <v>3</v>
-      </c>
-      <c r="I67" s="8">
-        <v>0</v>
-      </c>
-      <c r="J67" s="8">
-        <v>0</v>
-      </c>
-      <c r="K67" s="8">
-        <v>3</v>
-      </c>
-      <c r="L67" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
+      <c r="H87" s="8">
+        <v>3</v>
+      </c>
+      <c r="I87" s="8">
+        <v>0</v>
+      </c>
+      <c r="J87" s="8">
+        <v>0</v>
+      </c>
+      <c r="K87" s="8">
+        <v>3</v>
+      </c>
+      <c r="L87" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(ブロック外)</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F88" s="9"/>
+      <c r="G88" s="9"/>
+      <c r="H88" s="9">
+        <v>4</v>
+      </c>
+      <c r="I88" s="9">
+        <v>3</v>
+      </c>
+      <c r="J88" s="9">
+        <v>1</v>
+      </c>
+      <c r="K88" s="9">
+        <v>0</v>
+      </c>
+      <c r="L88" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aws</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F89" s="8">
+        <v>3</v>
+      </c>
+      <c r="G89" s="8">
+        <v>5</v>
+      </c>
+      <c r="H89" s="8">
+        <v>3</v>
+      </c>
+      <c r="I89" s="8">
+        <v>0</v>
+      </c>
+      <c r="J89" s="8">
+        <v>0</v>
+      </c>
+      <c r="K89" s="8">
+        <v>3</v>
+      </c>
+      <c r="L89" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">region</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F90" s="9">
+        <v>7</v>
+      </c>
+      <c r="G90" s="9">
+        <v>10</v>
+      </c>
+      <c r="H90" s="9">
+        <v>4</v>
+      </c>
+      <c r="I90" s="9">
+        <v>0</v>
+      </c>
+      <c r="J90" s="9">
+        <v>0</v>
+      </c>
+      <c r="K90" s="9">
+        <v>4</v>
+      </c>
+      <c r="L90" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/main.tf</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">variable</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image_tag</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F91" s="8">
+        <v>12</v>
+      </c>
+      <c r="G91" s="8">
+        <v>14</v>
+      </c>
+      <c r="H91" s="8">
+        <v>3</v>
+      </c>
+      <c r="I91" s="8">
+        <v>0</v>
+      </c>
+      <c r="J91" s="8">
+        <v>0</v>
+      </c>
+      <c r="K91" s="8">
+        <v>3</v>
+      </c>
+      <c r="L91" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63 件</t>
-        </is>
-      </c>
-      <c r="C68" s="16"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15">
-        <v>417</v>
-      </c>
-      <c r="I68" s="15">
-        <v>83</v>
-      </c>
-      <c r="J68" s="15">
-        <v>36</v>
-      </c>
-      <c r="K68" s="15">
-        <v>298</v>
-      </c>
-      <c r="L68" s="15">
-        <v>298</v>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87 件</t>
+        </is>
+      </c>
+      <c r="C92" s="16"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15">
+        <v>533</v>
+      </c>
+      <c r="I92" s="15">
+        <v>103</v>
+      </c>
+      <c r="J92" s="15">
+        <v>46</v>
+      </c>
+      <c r="K92" s="15">
+        <v>384</v>
+      </c>
+      <c r="L92" s="15">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L67"/>
+  <autoFilter ref="A4:L91"/>
   <mergeCells count="2">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="L5:L67">
+  <conditionalFormatting sqref="L5:L91">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -5827,7 +7664,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks 配下でファイル数が j1 より少ない環境について、j1 にのみ存在するファイルを j1 の実測値で推測しています</t>
+          <t xml:space="preserve">環境ディレクトリの配置先ごとに、ファイル数が j1 より少ない環境について、同じ配置先の j1 にのみ存在するファイルを j1 の実測値で推測しています</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -5896,33 +7733,33 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/compute/ec2.tf</t>
+          <t xml:space="preserve">scripts/cicd/app_release/build_stage/j2/push_image.sh</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D5" s="19">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E5" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" s="19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H5" s="19">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
@@ -5931,40 +7768,40 @@
       </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
+          <t xml:space="preserve">j2 のファイル数 1 &lt; j1 のファイル数 2 (参照: scripts/cicd/app_release/build_stage/j1/push_image.sh)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/j3/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j2/main.tf</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D6" s="21">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="21">
         <v>1</v>
       </c>
       <c r="G6" s="21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H6" s="21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
@@ -5973,19 +7810,19 @@
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
+          <t xml:space="preserve">j2 のファイル数 0 &lt; j1 のファイル数 2 (参照: terraform/stacks/03-dbrelease/env/j1/main.tf)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st</t>
+          <t xml:space="preserve">j2</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/compute/ec2.tf</t>
+          <t xml:space="preserve">terraform/stacks/03-dbrelease/env/j2/rds/cluster.tf</t>
         </is>
       </c>
       <c r="C7" s="26" t="inlineStr">
@@ -5994,19 +7831,19 @@
         </is>
       </c>
       <c r="D7" s="19">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E7" s="19">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F7" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H7" s="19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
@@ -6015,19 +7852,19 @@
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/compute/ec2.tf)</t>
+          <t xml:space="preserve">j2 のファイル数 0 &lt; j1 のファイル数 2 (参照: terraform/stacks/03-dbrelease/env/j1/rds/cluster.tf)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">st</t>
+          <t xml:space="preserve">j3</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/main.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -6036,19 +7873,19 @@
         </is>
       </c>
       <c r="D8" s="21">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E8" s="21">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F8" s="21">
         <v>1</v>
       </c>
       <c r="G8" s="21">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H8" s="21">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I8" s="27" t="inlineStr">
         <is>
@@ -6057,40 +7894,40 @@
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/main.tf)</t>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/compute/ec2.tf)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st</t>
+          <t xml:space="preserve">j3</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/network/subnet.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/j3/scripts/backup.sh</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">tf</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="D9" s="19">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E9" s="19">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F9" s="19">
         <v>1</v>
       </c>
       <c r="G9" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H9" s="19">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
@@ -6099,7 +7936,7 @@
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/subnet.tf)</t>
+          <t xml:space="preserve">j3 のファイル数 4 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/backup.sh)</t>
         </is>
       </c>
     </row>
@@ -6111,7 +7948,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/network/vpc.tf</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/compute/ec2.tf</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -6120,19 +7957,19 @@
         </is>
       </c>
       <c r="D10" s="21">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E10" s="21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G10" s="21">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="21">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" s="27" t="inlineStr">
         <is>
@@ -6141,7 +7978,7 @@
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/network/vpc.tf)</t>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/compute/ec2.tf)</t>
         </is>
       </c>
     </row>
@@ -6153,28 +7990,28 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/scripts/backup.sh</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/main.tf</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D11" s="19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E11" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="19">
         <v>1</v>
       </c>
       <c r="G11" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H11" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -6183,7 +8020,7 @@
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/backup.sh)</t>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/main.tf)</t>
         </is>
       </c>
     </row>
@@ -6195,77 +8032,245 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">terraform/stacks/st/scripts/deploy.sh</t>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/network/subnet.tf</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">tf</t>
         </is>
       </c>
       <c r="D12" s="21">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="21">
         <v>9</v>
       </c>
       <c r="F12" s="21">
+        <v>1</v>
+      </c>
+      <c r="G12" s="21">
+        <v>30</v>
+      </c>
+      <c r="H12" s="21">
+        <v>30</v>
+      </c>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/network/subnet.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/network/vpc.tf</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D13" s="19">
+        <v>59</v>
+      </c>
+      <c r="E13" s="19">
+        <v>10</v>
+      </c>
+      <c r="F13" s="19">
+        <v>9</v>
+      </c>
+      <c r="G13" s="19">
+        <v>40</v>
+      </c>
+      <c r="H13" s="19">
+        <v>40</v>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/network/vpc.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/scripts/backup.sh</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D14" s="21">
+        <v>17</v>
+      </c>
+      <c r="E14" s="21">
+        <v>4</v>
+      </c>
+      <c r="F14" s="21">
+        <v>1</v>
+      </c>
+      <c r="G14" s="21">
+        <v>12</v>
+      </c>
+      <c r="H14" s="21">
+        <v>12</v>
+      </c>
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/backup.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/01-workload/env/st/scripts/deploy.sh</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sh</t>
+        </is>
+      </c>
+      <c r="D15" s="19">
+        <v>43</v>
+      </c>
+      <c r="E15" s="19">
+        <v>9</v>
+      </c>
+      <c r="F15" s="19">
         <v>5</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G15" s="19">
         <v>29</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H15" s="19">
         <v>29</v>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">j1 の実測値</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/j1/scripts/deploy.sh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 0 &lt; j1 のファイル数 6 (参照: terraform/stacks/01-workload/env/j1/scripts/deploy.sh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">terraform/stacks/02-apprelease/env/st/ecs/service.tf</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tf</t>
+        </is>
+      </c>
+      <c r="D16" s="21">
+        <v>22</v>
+      </c>
+      <c r="E16" s="21">
+        <v>3</v>
+      </c>
+      <c r="F16" s="21">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21">
+        <v>18</v>
+      </c>
+      <c r="H16" s="21">
+        <v>18</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j1 の実測値</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st のファイル数 1 &lt; j1 のファイル数 2 (参照: terraform/stacks/02-apprelease/env/j1/ecs/service.tf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">合計</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8 件</t>
-        </is>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="15">
-        <v>266</v>
-      </c>
-      <c r="E13" s="15">
-        <v>56</v>
-      </c>
-      <c r="F13" s="15">
-        <v>20</v>
-      </c>
-      <c r="G13" s="15">
-        <v>190</v>
-      </c>
-      <c r="H13" s="15">
-        <v>190</v>
-      </c>
-      <c r="I13" s="16"/>
-      <c r="J13" s="14"/>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 件</t>
+        </is>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="15">
+        <v>332</v>
+      </c>
+      <c r="E17" s="15">
+        <v>68</v>
+      </c>
+      <c r="F17" s="15">
+        <v>29</v>
+      </c>
+      <c r="G17" s="15">
+        <v>235</v>
+      </c>
+      <c r="H17" s="15">
+        <v>235</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J12"/>
+  <autoFilter ref="A4:J16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H12">
+  <conditionalFormatting sqref="H5:H16">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
